--- a/research/traditional_assets/database/data/bermuda/bermuda_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/bermuda/bermuda_insurance_prop_cas.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ11"/>
+  <dimension ref="A1:AQ10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0689</v>
+        <v>0.02915</v>
       </c>
       <c r="E2">
-        <v>-0.08459999999999999</v>
+        <v>0.0677</v>
       </c>
       <c r="F2">
-        <v>0.9325</v>
+        <v>0.2</v>
       </c>
       <c r="G2">
-        <v>0.1293526312602192</v>
+        <v>0.1647087802584142</v>
       </c>
       <c r="H2">
-        <v>0.1293526312602192</v>
+        <v>0.1647087802584142</v>
       </c>
       <c r="I2">
-        <v>0.1536257712034958</v>
+        <v>0.07497865153415424</v>
       </c>
       <c r="J2">
-        <v>0.137740727874499</v>
+        <v>0.07333462994684631</v>
       </c>
       <c r="K2">
-        <v>2996.6</v>
+        <v>2411.8</v>
       </c>
       <c r="L2">
-        <v>0.129620818229793</v>
+        <v>0.1080144210314173</v>
       </c>
       <c r="M2">
-        <v>1791.7275</v>
+        <v>2654.26</v>
       </c>
       <c r="N2">
-        <v>0.04827333274060183</v>
+        <v>0.06162422193690985</v>
       </c>
       <c r="O2">
-        <v>0.597920142828539</v>
+        <v>1.100530723940625</v>
       </c>
       <c r="P2">
-        <v>376.1475</v>
+        <v>430.6</v>
       </c>
       <c r="Q2">
-        <v>0.01013429409720258</v>
+        <v>0.009997283599207834</v>
       </c>
       <c r="R2">
-        <v>0.1255247613962491</v>
+        <v>0.1785388506509661</v>
       </c>
       <c r="S2">
-        <v>1415.58</v>
+        <v>2223.66</v>
       </c>
       <c r="T2">
-        <v>0.7900643373504063</v>
+        <v>0.837770225976355</v>
       </c>
       <c r="U2">
-        <v>4699.5</v>
+        <v>4298.1</v>
       </c>
       <c r="V2">
-        <v>0.1266155301040244</v>
+        <v>0.09978942089585506</v>
       </c>
       <c r="W2">
-        <v>0.05241899870810704</v>
+        <v>0.01997242790683663</v>
       </c>
       <c r="X2">
-        <v>0.06536672379156305</v>
+        <v>0.104584021910588</v>
       </c>
       <c r="Y2">
-        <v>-0.01294772508345601</v>
+        <v>-0.08461159400375136</v>
       </c>
       <c r="Z2">
-        <v>0.6265011066049387</v>
+        <v>0.5755962863993855</v>
       </c>
       <c r="AA2">
-        <v>0.07915038231664193</v>
+        <v>-0.003937416481155233</v>
       </c>
       <c r="AB2">
-        <v>0.0580395736900135</v>
+        <v>0.09408612587018625</v>
       </c>
       <c r="AC2">
-        <v>0.02111080862662842</v>
+        <v>-0.09754969268071806</v>
       </c>
       <c r="AD2">
-        <v>8781.4</v>
+        <v>8586.799999999999</v>
       </c>
       <c r="AE2">
-        <v>556.6934808167143</v>
+        <v>482.9458960981841</v>
       </c>
       <c r="AF2">
-        <v>9338.093480816715</v>
+        <v>9069.745896098184</v>
       </c>
       <c r="AG2">
-        <v>4638.593480816715</v>
+        <v>4771.645896098184</v>
       </c>
       <c r="AH2">
-        <v>0.201016368552371</v>
+        <v>0.1739450400775496</v>
       </c>
       <c r="AI2">
-        <v>0.2079448196133109</v>
+        <v>0.2269271980560559</v>
       </c>
       <c r="AJ2">
-        <v>0.1110910145884531</v>
+        <v>0.09973478666105019</v>
       </c>
       <c r="AK2">
-        <v>0.1153675403826403</v>
+        <v>0.1337736653558055</v>
       </c>
       <c r="AL2">
-        <v>436.46</v>
+        <v>427.8</v>
       </c>
       <c r="AM2">
-        <v>436.46</v>
+        <v>427.8</v>
       </c>
       <c r="AN2">
-        <v>2.235767079377446</v>
+        <v>4.150919681918158</v>
       </c>
       <c r="AO2">
-        <v>8.160885304495258</v>
+        <v>3.889434315100514</v>
       </c>
       <c r="AP2">
-        <v>1.180997859000256</v>
+        <v>2.306647280157679</v>
       </c>
       <c r="AQ2">
-        <v>8.160885304495258</v>
+        <v>3.889434315100514</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SHL Holdings Ltd. (OTCPK:SYCR.F)</t>
+          <t>Arch Capital Group Ltd. (NasdaqGS:ACGL)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,14 +724,41 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
+      <c r="D3">
+        <v>0.113</v>
+      </c>
+      <c r="E3">
+        <v>0.21</v>
+      </c>
+      <c r="F3">
+        <v>0.167</v>
+      </c>
+      <c r="G3">
+        <v>0.2581668718029788</v>
+      </c>
+      <c r="H3">
+        <v>0.2581668718029788</v>
+      </c>
+      <c r="I3">
+        <v>0.1325553798236482</v>
+      </c>
+      <c r="J3">
+        <v>0.1270969766137602</v>
+      </c>
       <c r="K3">
-        <v>0</v>
+        <v>1240.5</v>
+      </c>
+      <c r="L3">
+        <v>0.1400761074537879</v>
       </c>
       <c r="M3">
-        <v>-0</v>
+        <v>947.9</v>
       </c>
       <c r="N3">
-        <v>-0</v>
+        <v>0.04111294240111034</v>
+      </c>
+      <c r="O3">
+        <v>0.7641273679967755</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -739,65 +766,83 @@
       <c r="Q3">
         <v>-0</v>
       </c>
+      <c r="R3">
+        <v>-0</v>
+      </c>
       <c r="S3">
-        <v>0</v>
+        <v>947.9</v>
+      </c>
+      <c r="T3">
+        <v>1</v>
       </c>
       <c r="U3">
-        <v>0</v>
+        <v>813.6</v>
       </c>
       <c r="V3">
-        <v>0</v>
+        <v>0.0352879944482998</v>
+      </c>
+      <c r="W3">
+        <v>0.09878558630300617</v>
       </c>
       <c r="X3">
-        <v>0.05604216204295502</v>
+        <v>0.09618063436963081</v>
+      </c>
+      <c r="Y3">
+        <v>0.002604951933375357</v>
       </c>
       <c r="Z3">
-        <v>0</v>
+        <v>0.5869532372276105</v>
       </c>
       <c r="AA3">
-        <v>0.7997101444434802</v>
+        <v>0.07459998186528845</v>
       </c>
       <c r="AB3">
-        <v>0.05545977861374444</v>
+        <v>0.09280074151269169</v>
       </c>
       <c r="AC3">
-        <v>0.7442503658297358</v>
+        <v>-0.01820075964740324</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>2725.2</v>
       </c>
       <c r="AE3">
-        <v>0.5001449697985615</v>
+        <v>114.0140590987687</v>
       </c>
       <c r="AF3">
-        <v>0.5001449697985615</v>
+        <v>2839.214059098768</v>
       </c>
       <c r="AG3">
-        <v>0.5001449697985615</v>
+        <v>2025.614059098768</v>
       </c>
       <c r="AH3">
-        <v>0.03268890398004812</v>
+        <v>0.1096424247592252</v>
       </c>
       <c r="AI3">
-        <v>1</v>
+        <v>0.1938928194069923</v>
       </c>
       <c r="AJ3">
-        <v>0.03268890398004812</v>
+        <v>0.08076091332582895</v>
       </c>
       <c r="AK3">
-        <v>1</v>
+        <v>0.146469312190681</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>130.8</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>130.8</v>
       </c>
       <c r="AN3">
-        <v>0</v>
+        <v>2.079829046783179</v>
+      </c>
+      <c r="AO3">
+        <v>8.906727828746176</v>
       </c>
       <c r="AP3">
-        <v>1.000289939597123</v>
+        <v>1.545916247499632</v>
+      </c>
+      <c r="AQ3">
+        <v>8.906727828746176</v>
       </c>
     </row>
     <row r="4">
@@ -808,7 +853,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Arch Capital Group Ltd. (NasdaqGS:ACGL)</t>
+          <t>Assured Guaranty Ltd. (NYSE:AGO)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -817,124 +862,121 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.163</v>
+        <v>-0.157</v>
       </c>
       <c r="E4">
-        <v>0.251</v>
-      </c>
-      <c r="F4">
-        <v>0.1</v>
+        <v>-0.197</v>
       </c>
       <c r="G4">
-        <v>0.2022787442254306</v>
+        <v>0.7323037323037324</v>
       </c>
       <c r="H4">
-        <v>0.2022787442254306</v>
+        <v>0.7323037323037324</v>
       </c>
       <c r="I4">
-        <v>0.2487025892486991</v>
+        <v>0.7039185143270795</v>
       </c>
       <c r="J4">
-        <v>0.2350962768082591</v>
+        <v>0.6226260874756583</v>
       </c>
       <c r="K4">
-        <v>2077.1</v>
+        <v>293</v>
       </c>
       <c r="L4">
-        <v>0.2226330964554058</v>
+        <v>0.3770913770913771</v>
       </c>
       <c r="M4">
-        <v>880.2</v>
+        <v>655</v>
       </c>
       <c r="N4">
-        <v>0.05150109122398469</v>
+        <v>0.1754620948298955</v>
       </c>
       <c r="O4">
-        <v>0.423763901593568</v>
+        <v>2.235494880546075</v>
       </c>
       <c r="P4">
-        <v>-0</v>
+        <v>64</v>
       </c>
       <c r="Q4">
-        <v>-0</v>
+        <v>0.01714438789177605</v>
       </c>
       <c r="R4">
-        <v>-0</v>
+        <v>0.2184300341296928</v>
       </c>
       <c r="S4">
-        <v>880.2</v>
+        <v>591</v>
       </c>
       <c r="T4">
-        <v>1</v>
+        <v>0.9022900763358779</v>
       </c>
       <c r="U4">
-        <v>1137.7</v>
+        <v>270</v>
       </c>
       <c r="V4">
-        <v>0.06656758859978117</v>
+        <v>0.07232788641843022</v>
       </c>
       <c r="W4">
-        <v>0.1779557916381083</v>
+        <v>0.04650793650793651</v>
       </c>
       <c r="X4">
-        <v>0.06132880560543444</v>
+        <v>0.1178943191338833</v>
       </c>
       <c r="Y4">
-        <v>0.1166269860326739</v>
+        <v>-0.07138638262594682</v>
       </c>
       <c r="Z4">
-        <v>0.6326851480463117</v>
+        <v>0.09543957795115889</v>
       </c>
       <c r="AA4">
-        <v>0.1487419226975701</v>
+        <v>0.05942317101005817</v>
       </c>
       <c r="AB4">
-        <v>0.0575813786366141</v>
+        <v>0.09858319722225775</v>
       </c>
       <c r="AC4">
-        <v>0.09116054406095596</v>
+        <v>-0.03916002621219958</v>
       </c>
       <c r="AD4">
-        <v>2724.1</v>
+        <v>1931</v>
       </c>
       <c r="AE4">
-        <v>134.8972654320606</v>
+        <v>115.2765718392957</v>
       </c>
       <c r="AF4">
-        <v>2858.99726543206</v>
+        <v>2046.276571839296</v>
       </c>
       <c r="AG4">
-        <v>1721.29726543206</v>
+        <v>1776.276571839296</v>
       </c>
       <c r="AH4">
-        <v>0.1433088715893266</v>
+        <v>0.3540714043363482</v>
       </c>
       <c r="AI4">
-        <v>0.1758647302264968</v>
+        <v>0.2834069514484023</v>
       </c>
       <c r="AJ4">
-        <v>0.09149900148001276</v>
+        <v>0.3224155746543467</v>
       </c>
       <c r="AK4">
-        <v>0.1138492090640618</v>
+        <v>0.2555691926039755</v>
       </c>
       <c r="AL4">
-        <v>145.6</v>
+        <v>80</v>
       </c>
       <c r="AM4">
-        <v>145.6</v>
+        <v>80</v>
       </c>
       <c r="AN4">
-        <v>1.127384844597111</v>
+        <v>3.323580034423408</v>
       </c>
       <c r="AO4">
-        <v>15.89972527472528</v>
+        <v>6.8375</v>
       </c>
       <c r="AP4">
-        <v>0.7123690209957623</v>
+        <v>3.05727465032581</v>
       </c>
       <c r="AQ4">
-        <v>15.89972527472528</v>
+        <v>6.8375</v>
       </c>
     </row>
     <row r="5">
@@ -954,121 +996,121 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.0553</v>
-      </c>
-      <c r="E5">
-        <v>-0.0394</v>
+        <v>0.038</v>
+      </c>
+      <c r="F5">
+        <v>0.2</v>
       </c>
       <c r="G5">
-        <v>0.02126474317107841</v>
+        <v>0.1532178704979335</v>
       </c>
       <c r="H5">
-        <v>0.02126474317107841</v>
+        <v>0.1532178704979335</v>
       </c>
       <c r="I5">
-        <v>0.1054761713743052</v>
+        <v>0.04586056346652791</v>
       </c>
       <c r="J5">
-        <v>0.09550179429869157</v>
+        <v>0.04500075202320666</v>
       </c>
       <c r="K5">
-        <v>416.5</v>
+        <v>379.5</v>
       </c>
       <c r="L5">
-        <v>0.08000691536363287</v>
+        <v>0.07469002164928164</v>
       </c>
       <c r="M5">
-        <v>156.7</v>
+        <v>197.4</v>
       </c>
       <c r="N5">
-        <v>0.03393537768537768</v>
+        <v>0.04304029304029305</v>
       </c>
       <c r="O5">
-        <v>0.3762304921968787</v>
+        <v>0.5201581027667984</v>
       </c>
       <c r="P5">
-        <v>145</v>
+        <v>148.5</v>
       </c>
       <c r="Q5">
-        <v>0.0314015939015939</v>
+        <v>0.03237833594976453</v>
       </c>
       <c r="R5">
-        <v>0.3481392557022809</v>
+        <v>0.391304347826087</v>
       </c>
       <c r="S5">
-        <v>11.69999999999999</v>
+        <v>48.90000000000001</v>
       </c>
       <c r="T5">
-        <v>0.0746649649010848</v>
+        <v>0.2477203647416414</v>
       </c>
       <c r="U5">
-        <v>947.5</v>
+        <v>1210.3</v>
       </c>
       <c r="V5">
-        <v>0.2051931739431739</v>
+        <v>0.2638888888888889</v>
       </c>
       <c r="W5">
-        <v>0.08831824254119044</v>
+        <v>0.07930868738375373</v>
       </c>
       <c r="X5">
-        <v>0.06723661452404273</v>
+        <v>0.1066718888272312</v>
       </c>
       <c r="Y5">
-        <v>0.02108162801714772</v>
+        <v>-0.02736320144347749</v>
       </c>
       <c r="Z5">
-        <v>0.9257947308520259</v>
+        <v>0.8897002190450862</v>
       </c>
       <c r="AA5">
-        <v>0.08841505794864271</v>
+        <v>0.04003717893224058</v>
       </c>
       <c r="AB5">
-        <v>0.05842054791820771</v>
+        <v>0.09455132181992909</v>
       </c>
       <c r="AC5">
-        <v>0.029994510030435</v>
+        <v>-0.05451414288768851</v>
       </c>
       <c r="AD5">
-        <v>1310.7</v>
+        <v>1393.2</v>
       </c>
       <c r="AE5">
-        <v>150.5607352982094</v>
+        <v>113.4123851328586</v>
       </c>
       <c r="AF5">
-        <v>1461.26073529821</v>
+        <v>1506.612385132859</v>
       </c>
       <c r="AG5">
-        <v>513.7607352982095</v>
+        <v>296.3123851328587</v>
       </c>
       <c r="AH5">
-        <v>0.2403839796514971</v>
+        <v>0.2472688860454379</v>
       </c>
       <c r="AI5">
-        <v>0.2150063529896037</v>
+        <v>0.2575400334128767</v>
       </c>
       <c r="AJ5">
-        <v>0.1001217341365403</v>
+        <v>0.06068602075254041</v>
       </c>
       <c r="AK5">
-        <v>0.0878394543056281</v>
+        <v>0.06386438652584148</v>
       </c>
       <c r="AL5">
-        <v>62.2</v>
+        <v>62.3</v>
       </c>
       <c r="AM5">
-        <v>62.2</v>
+        <v>62.3</v>
       </c>
       <c r="AN5">
-        <v>2.031463112213268</v>
+        <v>4.244972577696527</v>
       </c>
       <c r="AO5">
-        <v>8.945337620578778</v>
+        <v>3.730337078651686</v>
       </c>
       <c r="AP5">
-        <v>0.796281362830455</v>
+        <v>0.9028409053408248</v>
       </c>
       <c r="AQ5">
-        <v>8.945337620578778</v>
+        <v>3.730337078651686</v>
       </c>
     </row>
     <row r="6">
@@ -1088,121 +1130,121 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.0314</v>
-      </c>
-      <c r="E6">
-        <v>-0.121</v>
+        <v>0.09859999999999999</v>
+      </c>
+      <c r="F6">
+        <v>0.34</v>
       </c>
       <c r="G6">
-        <v>0.03866296980899569</v>
+        <v>-0.01651615969581749</v>
       </c>
       <c r="H6">
-        <v>0.03866296980899569</v>
+        <v>-0.01651615969581749</v>
       </c>
       <c r="I6">
-        <v>0.1785274183610598</v>
+        <v>-0.004039923954372623</v>
       </c>
       <c r="J6">
-        <v>0.1686331277049046</v>
+        <v>-0.004039923954372623</v>
       </c>
       <c r="K6">
-        <v>77.90000000000001</v>
+        <v>-35.5</v>
       </c>
       <c r="L6">
-        <v>0.1199938385705484</v>
+        <v>-0.04218155893536121</v>
       </c>
       <c r="M6">
-        <v>36.4</v>
+        <v>55</v>
       </c>
       <c r="N6">
-        <v>0.02106237703969448</v>
+        <v>0.02944010277272241</v>
       </c>
       <c r="O6">
-        <v>0.4672657252888318</v>
+        <v>-1.549295774647887</v>
       </c>
       <c r="P6">
         <v>36.4</v>
       </c>
       <c r="Q6">
-        <v>0.02106237703969448</v>
+        <v>0.01948399528958356</v>
       </c>
       <c r="R6">
-        <v>0.4672657252888318</v>
+        <v>-1.025352112676056</v>
       </c>
       <c r="S6">
-        <v>0</v>
+        <v>18.6</v>
       </c>
       <c r="T6">
-        <v>0</v>
+        <v>0.3381818181818182</v>
       </c>
       <c r="U6">
-        <v>563.4</v>
+        <v>390.6</v>
       </c>
       <c r="V6">
-        <v>0.3260039347297766</v>
+        <v>0.2090782571459159</v>
       </c>
       <c r="W6">
-        <v>0.05172299316114468</v>
+        <v>-0.02285015447991761</v>
       </c>
       <c r="X6">
-        <v>0.06536672379156305</v>
+        <v>0.1024961549939448</v>
       </c>
       <c r="Y6">
-        <v>-0.01364373063041837</v>
+        <v>-0.1253463094738624</v>
       </c>
       <c r="Z6">
-        <v>0.4793974302171025</v>
+        <v>0.578220542768808</v>
       </c>
       <c r="AA6">
-        <v>0.08084228807120374</v>
+        <v>-0.002335967021642048</v>
       </c>
       <c r="AB6">
-        <v>0.05798364347874253</v>
+        <v>0.09362092992044342</v>
       </c>
       <c r="AC6">
-        <v>0.0228586445924612</v>
+        <v>-0.09595689694208547</v>
       </c>
       <c r="AD6">
-        <v>465.3</v>
+        <v>461</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>465.3</v>
+        <v>461</v>
       </c>
       <c r="AG6">
-        <v>-98.09999999999997</v>
+        <v>70.39999999999998</v>
       </c>
       <c r="AH6">
-        <v>0.2121267380898108</v>
+        <v>0.1979220333161601</v>
       </c>
       <c r="AI6">
-        <v>0.2304606240713225</v>
+        <v>0.2513357321993239</v>
       </c>
       <c r="AJ6">
-        <v>-0.06018035703331082</v>
+        <v>0.03631486639843185</v>
       </c>
       <c r="AK6">
-        <v>-0.06739488870568834</v>
+        <v>0.04876697146023828</v>
       </c>
       <c r="AL6">
-        <v>22.3</v>
+        <v>14.3</v>
       </c>
       <c r="AM6">
-        <v>22.3</v>
+        <v>14.3</v>
       </c>
       <c r="AN6">
-        <v>4.000859845227859</v>
+        <v>-158.9655172413793</v>
       </c>
       <c r="AO6">
-        <v>5.197309417040358</v>
+        <v>-0.2377622377622377</v>
       </c>
       <c r="AP6">
-        <v>-0.8435081685296644</v>
+        <v>-24.27586206896551</v>
       </c>
       <c r="AQ6">
-        <v>5.197309417040358</v>
+        <v>-0.2377622377622377</v>
       </c>
     </row>
     <row r="7">
@@ -1213,7 +1255,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Argo Group International Holdings, Ltd. (NYSE:ARGO)</t>
+          <t>Hiscox Ltd (LSE:HSX)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1222,46 +1264,43 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.068</v>
-      </c>
-      <c r="E7">
-        <v>-0.0482</v>
+        <v>0.0197</v>
       </c>
       <c r="G7">
-        <v>0.01642662148169067</v>
+        <v>0.08816613002423936</v>
       </c>
       <c r="H7">
-        <v>0.01642662148169067</v>
+        <v>0.08816613002423936</v>
       </c>
       <c r="I7">
-        <v>0.08341542407937</v>
+        <v>-0.004269020657718607</v>
       </c>
       <c r="J7">
-        <v>0.07320005692762106</v>
+        <v>-0.004269020657718607</v>
       </c>
       <c r="K7">
-        <v>121.1</v>
+        <v>-16.6</v>
       </c>
       <c r="L7">
-        <v>0.05699896451096677</v>
+        <v>-0.006005571433739735</v>
       </c>
       <c r="M7">
-        <v>43.5</v>
+        <v>118.1</v>
       </c>
       <c r="N7">
-        <v>0.02146558105107328</v>
+        <v>0.02596060845863009</v>
       </c>
       <c r="O7">
-        <v>0.3592072667217176</v>
+        <v>-7.1144578313253</v>
       </c>
       <c r="P7">
-        <v>43.5</v>
+        <v>118.1</v>
       </c>
       <c r="Q7">
-        <v>0.02146558105107328</v>
+        <v>0.02596060845863009</v>
       </c>
       <c r="R7">
-        <v>0.3592072667217176</v>
+        <v>-7.1144578313253</v>
       </c>
       <c r="S7">
         <v>0</v>
@@ -1270,73 +1309,73 @@
         <v>0</v>
       </c>
       <c r="U7">
-        <v>202</v>
+        <v>1089.9</v>
       </c>
       <c r="V7">
-        <v>0.0996792499383173</v>
+        <v>0.2395805855974677</v>
       </c>
       <c r="W7">
-        <v>0.07038651554780587</v>
+        <v>-0.006563080694263235</v>
       </c>
       <c r="X7">
-        <v>0.06559857669672813</v>
+        <v>0.09755963769634016</v>
       </c>
       <c r="Y7">
-        <v>0.004787938851077742</v>
+        <v>-0.1041227183906034</v>
       </c>
       <c r="Z7">
-        <v>1.081288534992595</v>
+        <v>1.297455876830642</v>
       </c>
       <c r="AA7">
-        <v>0.07915038231664193</v>
+        <v>-0.005538865940668418</v>
       </c>
       <c r="AB7">
-        <v>0.0580395736900135</v>
+        <v>0.09360362247868224</v>
       </c>
       <c r="AC7">
-        <v>0.02111080862662842</v>
+        <v>-0.09914248841935067</v>
       </c>
       <c r="AD7">
-        <v>457.1</v>
+        <v>683</v>
       </c>
       <c r="AE7">
-        <v>100.3779500048525</v>
+        <v>0</v>
       </c>
       <c r="AF7">
-        <v>557.4779500048525</v>
+        <v>683</v>
       </c>
       <c r="AG7">
-        <v>355.4779500048525</v>
+        <v>-406.9000000000001</v>
       </c>
       <c r="AH7">
-        <v>0.2157440817185787</v>
+        <v>0.1305378234776958</v>
       </c>
       <c r="AI7">
-        <v>0.2280000725554562</v>
+        <v>0.2259046107031819</v>
       </c>
       <c r="AJ7">
-        <v>0.1492364570394651</v>
+        <v>-0.09823045168143306</v>
       </c>
       <c r="AK7">
-        <v>0.1584777515217799</v>
+        <v>-0.2104473752262736</v>
       </c>
       <c r="AL7">
-        <v>21.5</v>
+        <v>46.4</v>
       </c>
       <c r="AM7">
-        <v>21.5</v>
+        <v>46.4</v>
       </c>
       <c r="AN7">
-        <v>1.950917626973965</v>
+        <v>-220.3225806451613</v>
       </c>
       <c r="AO7">
-        <v>8.493023255813954</v>
+        <v>-0.2543103448275862</v>
       </c>
       <c r="AP7">
-        <v>1.517191421275512</v>
+        <v>131.2580645161291</v>
       </c>
       <c r="AQ7">
-        <v>8.493023255813954</v>
+        <v>-0.2543103448275862</v>
       </c>
     </row>
     <row r="8">
@@ -1347,7 +1386,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Assured Guaranty Ltd. (NYSE:AGO)</t>
+          <t>Argo Group International Holdings, Ltd. (NYSE:ARGO)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1356,121 +1395,118 @@
         </is>
       </c>
       <c r="D8">
-        <v>-0.132</v>
-      </c>
-      <c r="E8">
-        <v>-0.244</v>
+        <v>0.0203</v>
       </c>
       <c r="G8">
-        <v>0.458864426419467</v>
+        <v>0.08349545191650455</v>
       </c>
       <c r="H8">
-        <v>0.458864426419467</v>
+        <v>0.08349545191650455</v>
       </c>
       <c r="I8">
-        <v>0.466891875142989</v>
+        <v>-0.02518764583930563</v>
       </c>
       <c r="J8">
-        <v>0.4185927156454384</v>
+        <v>-0.02518764583930563</v>
       </c>
       <c r="K8">
-        <v>274</v>
+        <v>-181.3</v>
       </c>
       <c r="L8">
-        <v>0.3174971031286211</v>
+        <v>-0.09532572690467428</v>
       </c>
       <c r="M8">
-        <v>498</v>
+        <v>43.5</v>
       </c>
       <c r="N8">
-        <v>0.1421111206232343</v>
+        <v>0.0480026484219819</v>
       </c>
       <c r="O8">
-        <v>1.817518248175182</v>
+        <v>-0.2399338113623828</v>
       </c>
       <c r="P8">
-        <v>67</v>
+        <v>43.5</v>
       </c>
       <c r="Q8">
-        <v>0.0191193676340496</v>
+        <v>0.0480026484219819</v>
       </c>
       <c r="R8">
-        <v>0.2445255474452555</v>
+        <v>-0.2399338113623828</v>
       </c>
       <c r="S8">
-        <v>431</v>
+        <v>0</v>
       </c>
       <c r="T8">
-        <v>0.8654618473895582</v>
+        <v>0</v>
       </c>
       <c r="U8">
-        <v>239</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="V8">
-        <v>0.06820192335131124</v>
+        <v>0.1096888104171265</v>
       </c>
       <c r="W8">
-        <v>0.04183844861810963</v>
+        <v>-0.10398027070429</v>
       </c>
       <c r="X8">
-        <v>0.07821499075509278</v>
+        <v>0.1201652309204342</v>
       </c>
       <c r="Y8">
-        <v>-0.03637654213698314</v>
+        <v>-0.2241455016247242</v>
       </c>
       <c r="Z8">
-        <v>0.116380029909768</v>
+        <v>0.9139699012485918</v>
       </c>
       <c r="AA8">
-        <v>0.04871583276682712</v>
+        <v>-0.02302075018043467</v>
       </c>
       <c r="AB8">
-        <v>0.06163077101295912</v>
+        <v>0.09977005605635117</v>
       </c>
       <c r="AC8">
-        <v>-0.012914938246132</v>
+        <v>-0.1227908062367858</v>
       </c>
       <c r="AD8">
-        <v>1965</v>
+        <v>451.5</v>
       </c>
       <c r="AE8">
-        <v>115.3615587580023</v>
+        <v>85.52191810887686</v>
       </c>
       <c r="AF8">
-        <v>2080.361558758003</v>
+        <v>537.0219181088769</v>
       </c>
       <c r="AG8">
-        <v>1841.361558758003</v>
+        <v>437.6219181088769</v>
       </c>
       <c r="AH8">
-        <v>0.3725134525825524</v>
+        <v>0.3720993364711108</v>
       </c>
       <c r="AI8">
-        <v>0.2454309604819202</v>
+        <v>0.288423436496371</v>
       </c>
       <c r="AJ8">
-        <v>0.344459060589279</v>
+        <v>0.325654695917395</v>
       </c>
       <c r="AK8">
-        <v>0.2235377852026245</v>
+        <v>0.2482930360255773</v>
       </c>
       <c r="AL8">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="AM8">
-        <v>88</v>
+        <v>24</v>
       </c>
       <c r="AN8">
-        <v>4.486301369863014</v>
+        <v>-501.6666666666675</v>
       </c>
       <c r="AO8">
-        <v>4.625</v>
+        <v>-1.858333333333333</v>
       </c>
       <c r="AP8">
-        <v>4.204021823648407</v>
+        <v>-486.2465756765307</v>
       </c>
       <c r="AQ8">
-        <v>4.625</v>
+        <v>-1.858333333333333</v>
       </c>
     </row>
     <row r="9">
@@ -1481,7 +1517,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>White Mountains Insurance Group, Ltd. (NYSE:WTM)</t>
+          <t>James River Group Holdings, Ltd. (NasdaqGS:JRVR)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1490,121 +1526,118 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.0775</v>
-      </c>
-      <c r="E9">
-        <v>-0.239</v>
+        <v>0.006840000000000001</v>
       </c>
       <c r="G9">
-        <v>0.6461097167443528</v>
+        <v>-0.2260782094806991</v>
       </c>
       <c r="H9">
-        <v>0.6461097167443528</v>
+        <v>-0.2260782094806991</v>
       </c>
       <c r="I9">
-        <v>0.07769888386309047</v>
+        <v>-0.03687458087354664</v>
       </c>
       <c r="J9">
-        <v>0.07769888386309047</v>
+        <v>-0.03687458087354664</v>
       </c>
       <c r="K9">
-        <v>181</v>
+        <v>-53</v>
       </c>
       <c r="L9">
-        <v>0.162244532090355</v>
+        <v>-0.0666415189236766</v>
       </c>
       <c r="M9">
-        <v>90.3</v>
+        <v>18.36</v>
       </c>
       <c r="N9">
-        <v>0.02988779664382881</v>
+        <v>0.02343929528916125</v>
       </c>
       <c r="O9">
-        <v>0.4988950276243094</v>
+        <v>-0.3464150943396227</v>
       </c>
       <c r="P9">
-        <v>3.2</v>
+        <v>17.1</v>
       </c>
       <c r="Q9">
-        <v>0.001059146724919737</v>
+        <v>0.0218307162006894</v>
       </c>
       <c r="R9">
-        <v>0.01767955801104973</v>
+        <v>-0.3226415094339623</v>
       </c>
       <c r="S9">
-        <v>87.09999999999999</v>
+        <v>1.260000000000002</v>
       </c>
       <c r="T9">
-        <v>0.964562569213732</v>
+        <v>0.06862745098039223</v>
       </c>
       <c r="U9">
-        <v>214</v>
+        <v>187.5</v>
       </c>
       <c r="V9">
-        <v>0.07083043722900738</v>
+        <v>0.2393718881654538</v>
       </c>
       <c r="W9">
-        <v>0.0531150042550694</v>
+        <v>-0.0651425762045231</v>
       </c>
       <c r="X9">
-        <v>0.06462010434741562</v>
+        <v>0.1119530804526386</v>
       </c>
       <c r="Y9">
-        <v>-0.01150510009234622</v>
+        <v>-0.1770956566571617</v>
       </c>
       <c r="Z9">
-        <v>0.3548238135129863</v>
+        <v>1.007369681443214</v>
       </c>
       <c r="AA9">
-        <v>0.02756941427800439</v>
+        <v>-0.0371463347879367</v>
       </c>
       <c r="AB9">
-        <v>0.05779997661913751</v>
+        <v>0.09789830850826893</v>
       </c>
       <c r="AC9">
-        <v>-0.03023056234113312</v>
+        <v>-0.1350446432962056</v>
       </c>
       <c r="AD9">
-        <v>716.4</v>
+        <v>326.4</v>
       </c>
       <c r="AE9">
-        <v>40.09562581168141</v>
+        <v>11.88177084365821</v>
       </c>
       <c r="AF9">
-        <v>756.4956258116814</v>
+        <v>338.2817708436582</v>
       </c>
       <c r="AG9">
-        <v>542.4956258116814</v>
+        <v>150.7817708436582</v>
       </c>
       <c r="AH9">
-        <v>0.2002478960595291</v>
+        <v>0.3016113311017897</v>
       </c>
       <c r="AI9">
-        <v>0.171510015423231</v>
+        <v>0.3349384915740455</v>
       </c>
       <c r="AJ9">
-        <v>0.1522241123712373</v>
+        <v>0.1614224530979475</v>
       </c>
       <c r="AK9">
-        <v>0.1292642468637629</v>
+        <v>0.1833253649974445</v>
       </c>
       <c r="AL9">
-        <v>40.8</v>
+        <v>13.5</v>
       </c>
       <c r="AM9">
-        <v>40.8</v>
+        <v>13.5</v>
       </c>
       <c r="AN9">
-        <v>4.657997399219767</v>
+        <v>-14.66966292134831</v>
       </c>
       <c r="AO9">
-        <v>2.132352941176471</v>
+        <v>-2.303703703703704</v>
       </c>
       <c r="AP9">
-        <v>3.52727975170144</v>
+        <v>-6.776708801962166</v>
       </c>
       <c r="AQ9">
-        <v>2.132352941176471</v>
+        <v>-2.303703703703704</v>
       </c>
     </row>
     <row r="10">
@@ -1615,7 +1648,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Hiscox Ltd (LSE:HSX)</t>
+          <t>White Mountains Insurance Group, Ltd. (NYSE:WTM)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1624,252 +1657,121 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.0718</v>
-      </c>
-      <c r="F10">
-        <v>1.765</v>
+        <v>0.388</v>
+      </c>
+      <c r="E10">
+        <v>0.0677</v>
       </c>
       <c r="G10">
-        <v>-0.06418940923597993</v>
+        <v>-0.1257147213539681</v>
       </c>
       <c r="H10">
-        <v>-0.06418940923597993</v>
+        <v>-0.1257147213539681</v>
       </c>
       <c r="I10">
-        <v>0.01175665993616883</v>
+        <v>-0.1427672777425823</v>
       </c>
       <c r="J10">
-        <v>0.005878329968084414</v>
+        <v>-0.1427672777425823</v>
       </c>
       <c r="K10">
-        <v>-24.2</v>
+        <v>785.2</v>
       </c>
       <c r="L10">
-        <v>-0.007881195857487136</v>
+        <v>0.5986124876114965</v>
       </c>
       <c r="M10">
-        <v>41.2475</v>
+        <v>619</v>
       </c>
       <c r="N10">
-        <v>0.01021407522967585</v>
+        <v>0.1724522204268123</v>
       </c>
       <c r="O10">
-        <v>-1.704442148760331</v>
+        <v>0.7883341823739174</v>
       </c>
       <c r="P10">
-        <v>39.8475</v>
+        <v>3</v>
       </c>
       <c r="Q10">
-        <v>0.009867394695787832</v>
+        <v>0.0008357942831671031</v>
       </c>
       <c r="R10">
-        <v>-1.646590909090909</v>
+        <v>0.003820682628629648</v>
       </c>
       <c r="S10">
-        <v>1.399999999999999</v>
+        <v>616</v>
       </c>
       <c r="T10">
-        <v>0.03394145099703009</v>
+        <v>0.9951534733441034</v>
       </c>
       <c r="U10">
-        <v>1175.3</v>
+        <v>236.8</v>
       </c>
       <c r="V10">
-        <v>0.2910383081989946</v>
+        <v>0.06597202875132334</v>
       </c>
       <c r="W10">
-        <v>-0.009960487323016135</v>
+        <v>0.2229605020302695</v>
       </c>
       <c r="X10">
-        <v>0.06231800080242756</v>
+        <v>0.09925967221470011</v>
       </c>
       <c r="Y10">
-        <v>-0.0722784881254437</v>
+        <v>0.1237008298155694</v>
       </c>
       <c r="Z10">
-        <v>1.690579750041293</v>
+        <v>0.3863009455016282</v>
       </c>
       <c r="AA10">
-        <v>0.009937785608104389</v>
+        <v>-0.05515113437865309</v>
       </c>
       <c r="AB10">
-        <v>0.0581249484798286</v>
+        <v>0.0928114043713798</v>
       </c>
       <c r="AC10">
-        <v>-0.04818716287172421</v>
+        <v>-0.1479625387500329</v>
       </c>
       <c r="AD10">
-        <v>776.4</v>
+        <v>615.5</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>42.83919107472605</v>
       </c>
       <c r="AF10">
-        <v>776.4</v>
+        <v>658.339191074726</v>
       </c>
       <c r="AG10">
-        <v>-398.9</v>
+        <v>421.539191074726</v>
       </c>
       <c r="AH10">
-        <v>0.1612561530313415</v>
+        <v>0.1549857845458159</v>
       </c>
       <c r="AI10">
-        <v>0.2347889198016209</v>
+        <v>0.1455009257695866</v>
       </c>
       <c r="AJ10">
-        <v>-0.1096059790075287</v>
+        <v>0.1050973776946678</v>
       </c>
       <c r="AK10">
-        <v>-0.1871452029087497</v>
+        <v>0.09831040118112949</v>
       </c>
       <c r="AL10">
-        <v>47.3</v>
+        <v>56.5</v>
       </c>
       <c r="AM10">
-        <v>47.3</v>
+        <v>56.5</v>
       </c>
       <c r="AN10">
-        <v>14.78857142857143</v>
+        <v>-5.057518488085456</v>
       </c>
       <c r="AO10">
-        <v>0.7632135306553912</v>
+        <v>-3.355752212389381</v>
       </c>
       <c r="AP10">
-        <v>-7.598095238095238</v>
+        <v>-3.463756705626344</v>
       </c>
       <c r="AQ10">
-        <v>0.7632135306553912</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Bermuda</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>James River Group Holdings, Ltd. (NasdaqGS:JRVR)</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Insurance (Prop/Cas.)</t>
-        </is>
-      </c>
-      <c r="D11">
-        <v>0.0698</v>
-      </c>
-      <c r="G11">
-        <v>0.03817296301171515</v>
-      </c>
-      <c r="H11">
-        <v>0.03817296301171515</v>
-      </c>
-      <c r="I11">
-        <v>-0.1804528631149426</v>
-      </c>
-      <c r="J11">
-        <v>-0.1804528631149426</v>
-      </c>
-      <c r="K11">
-        <v>-126.8</v>
-      </c>
-      <c r="L11">
-        <v>-0.1669079899960511</v>
-      </c>
-      <c r="M11">
-        <v>45.38</v>
-      </c>
-      <c r="N11">
-        <v>0.04223752792256143</v>
-      </c>
-      <c r="O11">
-        <v>-0.3578864353312303</v>
-      </c>
-      <c r="P11">
-        <v>41.2</v>
-      </c>
-      <c r="Q11">
-        <v>0.0383469843633656</v>
-      </c>
-      <c r="R11">
-        <v>-0.3249211356466877</v>
-      </c>
-      <c r="S11">
-        <v>4.18</v>
-      </c>
-      <c r="T11">
-        <v>0.09211106214191273</v>
-      </c>
-      <c r="U11">
-        <v>220.6</v>
-      </c>
-      <c r="V11">
-        <v>0.2053239017125837</v>
-      </c>
-      <c r="W11">
-        <v>-0.1543705868030192</v>
-      </c>
-      <c r="X11">
-        <v>0.06875903827495405</v>
-      </c>
-      <c r="Y11">
-        <v>-0.2231296250779733</v>
-      </c>
-      <c r="Z11">
-        <v>0.9088405523856901</v>
-      </c>
-      <c r="AA11">
-        <v>-0.1640028797929637</v>
-      </c>
-      <c r="AB11">
-        <v>0.05996335128134745</v>
-      </c>
-      <c r="AC11">
-        <v>-0.2239662310743112</v>
-      </c>
-      <c r="AD11">
-        <v>366.4</v>
-      </c>
-      <c r="AE11">
-        <v>14.90020054210965</v>
-      </c>
-      <c r="AF11">
-        <v>381.3002005421096</v>
-      </c>
-      <c r="AG11">
-        <v>160.7002005421096</v>
-      </c>
-      <c r="AH11">
-        <v>0.2619359401064255</v>
-      </c>
-      <c r="AI11">
-        <v>0.319106315631313</v>
-      </c>
-      <c r="AJ11">
-        <v>0.1301110634356429</v>
-      </c>
-      <c r="AK11">
-        <v>0.1649391023964632</v>
-      </c>
-      <c r="AL11">
-        <v>8.76</v>
-      </c>
-      <c r="AM11">
-        <v>8.76</v>
-      </c>
-      <c r="AN11">
-        <v>-2.835693831746769</v>
-      </c>
-      <c r="AO11">
-        <v>-15.7648401826484</v>
-      </c>
-      <c r="AP11">
-        <v>-1.243713339076772</v>
-      </c>
-      <c r="AQ11">
-        <v>-15.7648401826484</v>
+        <v>-3.355752212389381</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/bermuda/bermuda_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/bermuda/bermuda_insurance_prop_cas.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ10"/>
+  <dimension ref="A1:AQ11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,124 +588,124 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.02915</v>
+        <v>0.0319</v>
       </c>
       <c r="E2">
-        <v>0.0677</v>
+        <v>0.258</v>
       </c>
       <c r="F2">
-        <v>0.2</v>
+        <v>0.166</v>
       </c>
       <c r="G2">
-        <v>0.1647087802584142</v>
+        <v>0.07782382926015911</v>
       </c>
       <c r="H2">
-        <v>0.1647087802584142</v>
+        <v>0.07782382926015911</v>
       </c>
       <c r="I2">
-        <v>0.07497865153415424</v>
+        <v>0.2538077512086553</v>
       </c>
       <c r="J2">
-        <v>0.07333462994684631</v>
+        <v>0.2205717640436976</v>
       </c>
       <c r="K2">
-        <v>2411.8</v>
+        <v>6796.6</v>
       </c>
       <c r="L2">
-        <v>0.1080144210314173</v>
+        <v>0.2158575897606911</v>
       </c>
       <c r="M2">
-        <v>2654.26</v>
+        <v>733.36</v>
       </c>
       <c r="N2">
-        <v>0.06162422193690985</v>
+        <v>0.01455125559541573</v>
       </c>
       <c r="O2">
-        <v>1.100530723940625</v>
+        <v>0.1079010093281935</v>
       </c>
       <c r="P2">
-        <v>430.6</v>
+        <v>421.33</v>
       </c>
       <c r="Q2">
-        <v>0.009997283599207834</v>
+        <v>0.008359987618654559</v>
       </c>
       <c r="R2">
-        <v>0.1785388506509661</v>
+        <v>0.06199128976252832</v>
       </c>
       <c r="S2">
-        <v>2223.66</v>
+        <v>312.03</v>
       </c>
       <c r="T2">
-        <v>0.837770225976355</v>
+        <v>0.4254799825460892</v>
       </c>
       <c r="U2">
-        <v>4298.1</v>
+        <v>5245.5</v>
       </c>
       <c r="V2">
-        <v>0.09978942089585506</v>
+        <v>0.1040806851011143</v>
       </c>
       <c r="W2">
-        <v>0.01997242790683663</v>
+        <v>0.1142748671222475</v>
       </c>
       <c r="X2">
-        <v>0.104584021910588</v>
+        <v>0.08688056413060978</v>
       </c>
       <c r="Y2">
-        <v>-0.08461159400375136</v>
+        <v>0.02739430299163777</v>
       </c>
       <c r="Z2">
-        <v>0.5755962863993855</v>
+        <v>0.9527920258319313</v>
       </c>
       <c r="AA2">
-        <v>-0.003937416481155233</v>
+        <v>0.1581287590605169</v>
       </c>
       <c r="AB2">
-        <v>0.09408612587018625</v>
+        <v>0.08041337062157548</v>
       </c>
       <c r="AC2">
-        <v>-0.09754969268071806</v>
+        <v>0.0770583777758433</v>
       </c>
       <c r="AD2">
-        <v>8586.799999999999</v>
+        <v>8527.1</v>
       </c>
       <c r="AE2">
-        <v>482.9458960981841</v>
+        <v>408.8612078433728</v>
       </c>
       <c r="AF2">
-        <v>9069.745896098184</v>
+        <v>8935.961207843373</v>
       </c>
       <c r="AG2">
-        <v>4771.645896098184</v>
+        <v>3690.461207843373</v>
       </c>
       <c r="AH2">
-        <v>0.1739450400775496</v>
+        <v>0.1506034787589848</v>
       </c>
       <c r="AI2">
-        <v>0.2269271980560559</v>
+        <v>0.187506682816135</v>
       </c>
       <c r="AJ2">
-        <v>0.09973478666105019</v>
+        <v>0.06822959710063599</v>
       </c>
       <c r="AK2">
-        <v>0.1337736653558055</v>
+        <v>0.08701606843893794</v>
       </c>
       <c r="AL2">
-        <v>427.8</v>
+        <v>506.1</v>
       </c>
       <c r="AM2">
-        <v>427.8</v>
+        <v>506.1</v>
       </c>
       <c r="AN2">
-        <v>4.150919681918158</v>
+        <v>1.030242400737484</v>
       </c>
       <c r="AO2">
-        <v>3.889434315100514</v>
+        <v>15.76882039122703</v>
       </c>
       <c r="AP2">
-        <v>2.306647280157679</v>
+        <v>0.4458807349036732</v>
       </c>
       <c r="AQ2">
-        <v>3.889434315100514</v>
+        <v>15.76882039122703</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Arch Capital Group Ltd. (NasdaqGS:ACGL)</t>
+          <t>Fidelis Insurance Holdings Limited (NYSE:FIHL)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,125 +724,110 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.113</v>
-      </c>
-      <c r="E3">
-        <v>0.21</v>
-      </c>
-      <c r="F3">
-        <v>0.167</v>
-      </c>
       <c r="G3">
-        <v>0.2581668718029788</v>
+        <v>0.03242605593278858</v>
       </c>
       <c r="H3">
-        <v>0.2581668718029788</v>
+        <v>0.03242605593278858</v>
       </c>
       <c r="I3">
-        <v>0.1325553798236482</v>
+        <v>0.5995982820866217</v>
       </c>
       <c r="J3">
-        <v>0.1270969766137602</v>
+        <v>0.5910538388858347</v>
       </c>
       <c r="K3">
-        <v>1240.5</v>
+        <v>2024.1</v>
       </c>
       <c r="L3">
-        <v>0.1400761074537879</v>
+        <v>0.58237426631373</v>
       </c>
       <c r="M3">
-        <v>947.9</v>
+        <v>85.2</v>
       </c>
       <c r="N3">
-        <v>0.04111294240111034</v>
+        <v>0.0570281124497992</v>
       </c>
       <c r="O3">
-        <v>0.7641273679967755</v>
+        <v>0.04209278197717504</v>
       </c>
       <c r="P3">
-        <v>-0</v>
+        <v>34.6</v>
       </c>
       <c r="Q3">
-        <v>-0</v>
+        <v>0.02315930388219545</v>
       </c>
       <c r="R3">
-        <v>-0</v>
+        <v>0.0170940170940171</v>
       </c>
       <c r="S3">
-        <v>947.9</v>
+        <v>50.6</v>
       </c>
       <c r="T3">
-        <v>1</v>
+        <v>0.5938967136150235</v>
       </c>
       <c r="U3">
-        <v>813.6</v>
+        <v>569</v>
       </c>
       <c r="V3">
-        <v>0.0352879944482998</v>
-      </c>
-      <c r="W3">
-        <v>0.09878558630300617</v>
+        <v>0.3808567603748327</v>
       </c>
       <c r="X3">
-        <v>0.09618063436963081</v>
-      </c>
-      <c r="Y3">
-        <v>0.002604951933375357</v>
+        <v>0.0911794867564116</v>
       </c>
       <c r="Z3">
-        <v>0.5869532372276105</v>
+        <v>117.0982678668811</v>
       </c>
       <c r="AA3">
-        <v>0.07459998186528845</v>
+        <v>69.2113807496019</v>
       </c>
       <c r="AB3">
-        <v>0.09280074151269169</v>
+        <v>0.08367035517866658</v>
       </c>
       <c r="AC3">
-        <v>-0.01820075964740324</v>
+        <v>69.12771039442323</v>
       </c>
       <c r="AD3">
-        <v>2725.2</v>
+        <v>506.4</v>
       </c>
       <c r="AE3">
-        <v>114.0140590987687</v>
+        <v>29.68105389868882</v>
       </c>
       <c r="AF3">
-        <v>2839.214059098768</v>
+        <v>536.0810538986888</v>
       </c>
       <c r="AG3">
-        <v>2025.614059098768</v>
+        <v>-32.91894610131123</v>
       </c>
       <c r="AH3">
-        <v>0.1096424247592252</v>
+        <v>0.2640687931494985</v>
       </c>
       <c r="AI3">
-        <v>0.1938928194069923</v>
+        <v>0.1988297681728433</v>
       </c>
       <c r="AJ3">
-        <v>0.08076091332582895</v>
+        <v>-0.02253054066608534</v>
       </c>
       <c r="AK3">
-        <v>0.146469312190681</v>
+        <v>-0.01547538515397057</v>
       </c>
       <c r="AL3">
-        <v>130.8</v>
+        <v>34.8</v>
       </c>
       <c r="AM3">
-        <v>130.8</v>
+        <v>34.8</v>
       </c>
       <c r="AN3">
-        <v>2.079829046783179</v>
+        <v>0.2421576128538638</v>
       </c>
       <c r="AO3">
-        <v>8.906727828746176</v>
+        <v>59.98275862068967</v>
       </c>
       <c r="AP3">
-        <v>1.545916247499632</v>
+        <v>-0.01574165364446788</v>
       </c>
       <c r="AQ3">
-        <v>8.906727828746176</v>
+        <v>59.98275862068967</v>
       </c>
     </row>
     <row r="4">
@@ -853,7 +838,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Assured Guaranty Ltd. (NYSE:AGO)</t>
+          <t>Hamilton Insurance Group, Ltd. (NYSE:HG)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -861,122 +846,113 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
-      <c r="D4">
-        <v>-0.157</v>
-      </c>
-      <c r="E4">
-        <v>-0.197</v>
+      <c r="F4">
+        <v>0.54</v>
       </c>
       <c r="G4">
-        <v>0.7323037323037324</v>
+        <v>0.0162480435268689</v>
       </c>
       <c r="H4">
-        <v>0.7323037323037324</v>
+        <v>0.0162480435268689</v>
       </c>
       <c r="I4">
-        <v>0.7039185143270795</v>
+        <v>0.1147066134091181</v>
       </c>
       <c r="J4">
-        <v>0.6226260874756583</v>
+        <v>0.106345614478137</v>
       </c>
       <c r="K4">
-        <v>293</v>
+        <v>72.8</v>
       </c>
       <c r="L4">
-        <v>0.3770913770913771</v>
+        <v>0.05425952150257136</v>
       </c>
       <c r="M4">
-        <v>655</v>
+        <v>2.25</v>
       </c>
       <c r="N4">
-        <v>0.1754620948298955</v>
+        <v>0.001368363437328955</v>
       </c>
       <c r="O4">
-        <v>2.235494880546075</v>
+        <v>0.03090659340659341</v>
       </c>
       <c r="P4">
-        <v>64</v>
+        <v>-0</v>
       </c>
       <c r="Q4">
-        <v>0.01714438789177605</v>
+        <v>-0</v>
       </c>
       <c r="R4">
-        <v>0.2184300341296928</v>
+        <v>-0</v>
       </c>
       <c r="S4">
-        <v>591</v>
+        <v>2.25</v>
       </c>
       <c r="T4">
-        <v>0.9022900763358779</v>
+        <v>1</v>
       </c>
       <c r="U4">
-        <v>270</v>
+        <v>804.5</v>
       </c>
       <c r="V4">
-        <v>0.07232788641843022</v>
-      </c>
-      <c r="W4">
-        <v>0.04650793650793651</v>
+        <v>0.489265949036064</v>
       </c>
       <c r="X4">
-        <v>0.1178943191338833</v>
-      </c>
-      <c r="Y4">
-        <v>-0.07138638262594682</v>
+        <v>0.08104096098985894</v>
       </c>
       <c r="Z4">
-        <v>0.09543957795115889</v>
+        <v>173.330936845521</v>
       </c>
       <c r="AA4">
-        <v>0.05942317101005817</v>
+        <v>18.43298498690809</v>
       </c>
       <c r="AB4">
-        <v>0.09858319722225775</v>
+        <v>0.07944113076462764</v>
       </c>
       <c r="AC4">
-        <v>-0.03916002621219958</v>
+        <v>18.35354385614346</v>
       </c>
       <c r="AD4">
-        <v>1931</v>
+        <v>149.8</v>
       </c>
       <c r="AE4">
-        <v>115.2765718392957</v>
+        <v>7.740683944931154</v>
       </c>
       <c r="AF4">
-        <v>2046.276571839296</v>
+        <v>157.5406839449312</v>
       </c>
       <c r="AG4">
-        <v>1776.276571839296</v>
+        <v>-646.9593160550688</v>
       </c>
       <c r="AH4">
-        <v>0.3540714043363482</v>
+        <v>0.08743319281703266</v>
       </c>
       <c r="AI4">
-        <v>0.2834069514484023</v>
+        <v>0.08048299253054826</v>
       </c>
       <c r="AJ4">
-        <v>0.3224155746543467</v>
+        <v>-0.6486843728223877</v>
       </c>
       <c r="AK4">
-        <v>0.2555691926039755</v>
+        <v>-0.5611384220057327</v>
       </c>
       <c r="AL4">
-        <v>80</v>
+        <v>20.5</v>
       </c>
       <c r="AM4">
-        <v>80</v>
+        <v>20.5</v>
       </c>
       <c r="AN4">
-        <v>3.323580034423408</v>
+        <v>0.8929955290611029</v>
       </c>
       <c r="AO4">
-        <v>6.8375</v>
+        <v>7.44390243902439</v>
       </c>
       <c r="AP4">
-        <v>3.05727465032581</v>
+        <v>-3.8566874280481</v>
       </c>
       <c r="AQ4">
-        <v>6.8375</v>
+        <v>7.44390243902439</v>
       </c>
     </row>
     <row r="5">
@@ -987,7 +963,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>AXIS Capital Holdings Limited (NYSE:AXS)</t>
+          <t>Arch Capital Group Ltd. (NasdaqGS:ACGL)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -996,121 +972,121 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.038</v>
+        <v>0.182</v>
+      </c>
+      <c r="E5">
+        <v>0.288</v>
       </c>
       <c r="F5">
-        <v>0.2</v>
+        <v>0.166</v>
       </c>
       <c r="G5">
-        <v>0.1532178704979335</v>
+        <v>0.1276410248354514</v>
       </c>
       <c r="H5">
-        <v>0.1532178704979335</v>
+        <v>0.1276410248354514</v>
       </c>
       <c r="I5">
-        <v>0.04586056346652791</v>
+        <v>0.2596547622448285</v>
       </c>
       <c r="J5">
-        <v>0.04500075202320666</v>
+        <v>0.2384676270428025</v>
       </c>
       <c r="K5">
-        <v>379.5</v>
+        <v>2968.9</v>
       </c>
       <c r="L5">
-        <v>0.07469002164928164</v>
+        <v>0.2331877660660708</v>
       </c>
       <c r="M5">
-        <v>197.4</v>
+        <v>-0</v>
       </c>
       <c r="N5">
-        <v>0.04304029304029305</v>
+        <v>-0</v>
       </c>
       <c r="O5">
-        <v>0.5201581027667984</v>
+        <v>-0</v>
       </c>
       <c r="P5">
-        <v>148.5</v>
+        <v>-0</v>
       </c>
       <c r="Q5">
-        <v>0.03237833594976453</v>
+        <v>-0</v>
       </c>
       <c r="R5">
-        <v>0.391304347826087</v>
+        <v>-0</v>
       </c>
       <c r="S5">
-        <v>48.90000000000001</v>
-      </c>
-      <c r="T5">
-        <v>0.2477203647416414</v>
+        <v>0</v>
       </c>
       <c r="U5">
-        <v>1210.3</v>
+        <v>859</v>
       </c>
       <c r="V5">
-        <v>0.2638888888888889</v>
+        <v>0.03117446814687929</v>
       </c>
       <c r="W5">
-        <v>0.07930868738375373</v>
+        <v>0.2707590446051564</v>
       </c>
       <c r="X5">
-        <v>0.1066718888272312</v>
+        <v>0.08135660235778322</v>
       </c>
       <c r="Y5">
-        <v>-0.02736320144347749</v>
+        <v>0.1894024422473732</v>
       </c>
       <c r="Z5">
-        <v>0.8897002190450862</v>
+        <v>0.9195066933013329</v>
       </c>
       <c r="AA5">
-        <v>0.04003717893224058</v>
+        <v>0.2192725792015429</v>
       </c>
       <c r="AB5">
-        <v>0.09455132181992909</v>
+        <v>0.07935176584332879</v>
       </c>
       <c r="AC5">
-        <v>-0.05451414288768851</v>
+        <v>0.1399208133582141</v>
       </c>
       <c r="AD5">
-        <v>1393.2</v>
+        <v>2726</v>
       </c>
       <c r="AE5">
-        <v>113.4123851328586</v>
+        <v>139.637490256466</v>
       </c>
       <c r="AF5">
-        <v>1506.612385132859</v>
+        <v>2865.637490256466</v>
       </c>
       <c r="AG5">
-        <v>296.3123851328587</v>
+        <v>2006.637490256466</v>
       </c>
       <c r="AH5">
-        <v>0.2472688860454379</v>
+        <v>0.09420168041667405</v>
       </c>
       <c r="AI5">
-        <v>0.2575400334128767</v>
+        <v>0.1582644757646759</v>
       </c>
       <c r="AJ5">
-        <v>0.06068602075254041</v>
+        <v>0.06788069988334772</v>
       </c>
       <c r="AK5">
-        <v>0.06386438652584148</v>
+        <v>0.1163427449927595</v>
       </c>
       <c r="AL5">
-        <v>62.3</v>
+        <v>130.3</v>
       </c>
       <c r="AM5">
-        <v>62.3</v>
+        <v>130.3</v>
       </c>
       <c r="AN5">
-        <v>4.244972577696527</v>
+        <v>0.7945205479452054</v>
       </c>
       <c r="AO5">
-        <v>3.730337078651686</v>
+        <v>25.3407521105142</v>
       </c>
       <c r="AP5">
-        <v>0.9028409053408248</v>
+        <v>0.5848549957028465</v>
       </c>
       <c r="AQ5">
-        <v>3.730337078651686</v>
+        <v>25.3407521105142</v>
       </c>
     </row>
     <row r="6">
@@ -1121,7 +1097,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Lancashire Holdings Limited (LSE:LRE)</t>
+          <t>Hiscox Ltd (LSE:HSX)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1130,121 +1106,124 @@
         </is>
       </c>
       <c r="D6">
-        <v>0.09859999999999999</v>
+        <v>0.0319</v>
+      </c>
+      <c r="E6">
+        <v>0.345</v>
       </c>
       <c r="F6">
-        <v>0.34</v>
+        <v>0.08</v>
       </c>
       <c r="G6">
-        <v>-0.01651615969581749</v>
+        <v>0.02247482949009419</v>
       </c>
       <c r="H6">
-        <v>-0.01651615969581749</v>
+        <v>0.02247482949009419</v>
       </c>
       <c r="I6">
-        <v>-0.004039923954372623</v>
+        <v>0.1196817148424813</v>
       </c>
       <c r="J6">
-        <v>-0.004039923954372623</v>
+        <v>0.1087709214091119</v>
       </c>
       <c r="K6">
-        <v>-35.5</v>
+        <v>258.2</v>
       </c>
       <c r="L6">
-        <v>-0.04218155893536121</v>
+        <v>0.08385839558298148</v>
       </c>
       <c r="M6">
-        <v>55</v>
+        <v>122.6</v>
       </c>
       <c r="N6">
-        <v>0.02944010277272241</v>
+        <v>0.02630393271685726</v>
       </c>
       <c r="O6">
-        <v>-1.549295774647887</v>
+        <v>0.4748257164988381</v>
       </c>
       <c r="P6">
-        <v>36.4</v>
+        <v>122.6</v>
       </c>
       <c r="Q6">
-        <v>0.01948399528958356</v>
+        <v>0.02630393271685726</v>
       </c>
       <c r="R6">
-        <v>-1.025352112676056</v>
+        <v>0.4748257164988381</v>
       </c>
       <c r="S6">
-        <v>18.6</v>
+        <v>0</v>
       </c>
       <c r="T6">
-        <v>0.3381818181818182</v>
+        <v>0</v>
       </c>
       <c r="U6">
-        <v>390.6</v>
+        <v>992.4</v>
       </c>
       <c r="V6">
-        <v>0.2090782571459159</v>
+        <v>0.2129202514535819</v>
       </c>
       <c r="W6">
-        <v>-0.02285015447991761</v>
+        <v>0.1103748984739024</v>
       </c>
       <c r="X6">
-        <v>0.1024961549939448</v>
+        <v>0.0830724982292857</v>
       </c>
       <c r="Y6">
-        <v>-0.1253463094738624</v>
+        <v>0.02730240024461673</v>
       </c>
       <c r="Z6">
-        <v>0.578220542768808</v>
+        <v>1.59335541295798</v>
       </c>
       <c r="AA6">
-        <v>-0.002335967021642048</v>
+        <v>0.1733107363996354</v>
       </c>
       <c r="AB6">
-        <v>0.09362092992044342</v>
+        <v>0.08027112783870591</v>
       </c>
       <c r="AC6">
-        <v>-0.09595689694208547</v>
+        <v>0.09303960856092947</v>
       </c>
       <c r="AD6">
-        <v>461</v>
+        <v>692.2</v>
       </c>
       <c r="AE6">
         <v>0</v>
       </c>
       <c r="AF6">
-        <v>461</v>
+        <v>692.2</v>
       </c>
       <c r="AG6">
-        <v>70.39999999999998</v>
+        <v>-300.1999999999999</v>
       </c>
       <c r="AH6">
-        <v>0.1979220333161601</v>
+        <v>0.129308251293643</v>
       </c>
       <c r="AI6">
-        <v>0.2513357321993239</v>
+        <v>0.1956749116607774</v>
       </c>
       <c r="AJ6">
-        <v>0.03631486639843185</v>
+        <v>-0.06884215836906918</v>
       </c>
       <c r="AK6">
-        <v>0.04876697146023828</v>
+        <v>-0.1179521433342501</v>
       </c>
       <c r="AL6">
-        <v>14.3</v>
+        <v>53.7</v>
       </c>
       <c r="AM6">
-        <v>14.3</v>
+        <v>53.7</v>
       </c>
       <c r="AN6">
-        <v>-158.9655172413793</v>
+        <v>1.832186341979884</v>
       </c>
       <c r="AO6">
-        <v>-0.2377622377622377</v>
+        <v>6.862197392923649</v>
       </c>
       <c r="AP6">
-        <v>-24.27586206896551</v>
+        <v>-0.7946003176283746</v>
       </c>
       <c r="AQ6">
-        <v>-0.2377622377622377</v>
+        <v>6.862197392923649</v>
       </c>
     </row>
     <row r="7">
@@ -1255,7 +1234,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Hiscox Ltd (LSE:HSX)</t>
+          <t>AXIS Capital Holdings Limited (NYSE:AXS)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1264,118 +1243,124 @@
         </is>
       </c>
       <c r="D7">
-        <v>0.0197</v>
+        <v>0.0152</v>
+      </c>
+      <c r="E7">
+        <v>0.228</v>
+      </c>
+      <c r="F7">
+        <v>0.2</v>
       </c>
       <c r="G7">
-        <v>0.08816613002423936</v>
+        <v>0.04420834967378516</v>
       </c>
       <c r="H7">
-        <v>0.08816613002423936</v>
+        <v>0.04420834967378516</v>
       </c>
       <c r="I7">
-        <v>-0.004269020657718607</v>
+        <v>0.1489329678327353</v>
       </c>
       <c r="J7">
-        <v>-0.004269020657718607</v>
+        <v>0.1274963276226524</v>
       </c>
       <c r="K7">
-        <v>-16.6</v>
+        <v>567.4</v>
       </c>
       <c r="L7">
-        <v>-0.006005571433739735</v>
+        <v>0.1011444258262327</v>
       </c>
       <c r="M7">
-        <v>118.1</v>
+        <v>169.7</v>
       </c>
       <c r="N7">
-        <v>0.02596060845863009</v>
+        <v>0.03595491334378575</v>
       </c>
       <c r="O7">
-        <v>-7.1144578313253</v>
+        <v>0.2990835389495946</v>
       </c>
       <c r="P7">
-        <v>118.1</v>
+        <v>152</v>
       </c>
       <c r="Q7">
-        <v>0.02596060845863009</v>
+        <v>0.0322047544387474</v>
       </c>
       <c r="R7">
-        <v>-7.1144578313253</v>
+        <v>0.2678886147338738</v>
       </c>
       <c r="S7">
-        <v>0</v>
+        <v>17.69999999999999</v>
       </c>
       <c r="T7">
-        <v>0</v>
+        <v>0.1043017088980553</v>
       </c>
       <c r="U7">
-        <v>1089.9</v>
+        <v>889.6</v>
       </c>
       <c r="V7">
-        <v>0.2395805855974677</v>
+        <v>0.1884825628204585</v>
       </c>
       <c r="W7">
-        <v>-0.006563080694263235</v>
+        <v>0.1495755786365793</v>
       </c>
       <c r="X7">
-        <v>0.09755963769634016</v>
+        <v>0.08957142418518964</v>
       </c>
       <c r="Y7">
-        <v>-0.1041227183906034</v>
+        <v>0.06000415445138967</v>
       </c>
       <c r="Z7">
-        <v>1.297455876830642</v>
+        <v>1.240261284454612</v>
       </c>
       <c r="AA7">
-        <v>-0.005538865940668418</v>
+        <v>0.1581287590605169</v>
       </c>
       <c r="AB7">
-        <v>0.09360362247868224</v>
+        <v>0.08107038128467357</v>
       </c>
       <c r="AC7">
-        <v>-0.09914248841935067</v>
+        <v>0.0770583777758433</v>
       </c>
       <c r="AD7">
-        <v>683</v>
+        <v>1399.1</v>
       </c>
       <c r="AE7">
-        <v>0</v>
+        <v>97.57918525960783</v>
       </c>
       <c r="AF7">
-        <v>683</v>
+        <v>1496.679185259608</v>
       </c>
       <c r="AG7">
-        <v>-406.9000000000001</v>
+        <v>607.0791852596077</v>
       </c>
       <c r="AH7">
-        <v>0.1305378234776958</v>
+        <v>0.2407599447623831</v>
       </c>
       <c r="AI7">
-        <v>0.2259046107031819</v>
+        <v>0.2292047284179737</v>
       </c>
       <c r="AJ7">
-        <v>-0.09823045168143306</v>
+        <v>0.1139652626137083</v>
       </c>
       <c r="AK7">
-        <v>-0.2104473752262736</v>
+        <v>0.1076328254895888</v>
       </c>
       <c r="AL7">
-        <v>46.4</v>
+        <v>66.5</v>
       </c>
       <c r="AM7">
-        <v>46.4</v>
+        <v>66.5</v>
       </c>
       <c r="AN7">
-        <v>-220.3225806451613</v>
+        <v>1.499249892841835</v>
       </c>
       <c r="AO7">
-        <v>-0.2543103448275862</v>
+        <v>12.5593984962406</v>
       </c>
       <c r="AP7">
-        <v>131.2580645161291</v>
+        <v>0.6505349177664035</v>
       </c>
       <c r="AQ7">
-        <v>-0.2543103448275862</v>
+        <v>12.5593984962406</v>
       </c>
     </row>
     <row r="8">
@@ -1386,7 +1371,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Argo Group International Holdings, Ltd. (NYSE:ARGO)</t>
+          <t>James River Group Holdings, Ltd. (NasdaqGS:JRVR)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1395,118 +1380,124 @@
         </is>
       </c>
       <c r="D8">
-        <v>0.0203</v>
+        <v>0.00658</v>
+      </c>
+      <c r="E8">
+        <v>0.028</v>
+      </c>
+      <c r="F8">
+        <v>0.06900000000000001</v>
       </c>
       <c r="G8">
-        <v>0.08349545191650455</v>
+        <v>0.08054860128442363</v>
       </c>
       <c r="H8">
-        <v>0.08349545191650455</v>
+        <v>0.08054860128442363</v>
       </c>
       <c r="I8">
-        <v>-0.02518764583930563</v>
+        <v>0.1348872146945039</v>
       </c>
       <c r="J8">
-        <v>-0.02518764583930563</v>
+        <v>0.09206587669624867</v>
       </c>
       <c r="K8">
-        <v>-181.3</v>
+        <v>60.2</v>
       </c>
       <c r="L8">
-        <v>-0.09532572690467428</v>
+        <v>0.06552737563949058</v>
       </c>
       <c r="M8">
-        <v>43.5</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="N8">
-        <v>0.0480026484219819</v>
+        <v>0.02763082231167337</v>
       </c>
       <c r="O8">
-        <v>-0.2399338113623828</v>
+        <v>0.1596345514950166</v>
       </c>
       <c r="P8">
-        <v>43.5</v>
+        <v>7.73</v>
       </c>
       <c r="Q8">
-        <v>0.0480026484219819</v>
+        <v>0.02222541690626797</v>
       </c>
       <c r="R8">
-        <v>-0.2399338113623828</v>
+        <v>0.1284053156146179</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.879999999999999</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>0.1956295525494276</v>
       </c>
       <c r="U8">
-        <v>99.40000000000001</v>
+        <v>232.9</v>
       </c>
       <c r="V8">
-        <v>0.1096888104171265</v>
+        <v>0.6696377228292122</v>
       </c>
       <c r="W8">
-        <v>-0.10398027070429</v>
+        <v>0.1142748671222475</v>
       </c>
       <c r="X8">
-        <v>0.1201652309204342</v>
+        <v>0.1144762461273379</v>
       </c>
       <c r="Y8">
-        <v>-0.2241455016247242</v>
+        <v>-0.000201379005090388</v>
       </c>
       <c r="Z8">
-        <v>0.9139699012485918</v>
+        <v>1.441334125674022</v>
       </c>
       <c r="AA8">
-        <v>-0.02302075018043467</v>
+        <v>0.1326976898923999</v>
       </c>
       <c r="AB8">
-        <v>0.09977005605635117</v>
+        <v>0.0877853301421843</v>
       </c>
       <c r="AC8">
-        <v>-0.1227908062367858</v>
+        <v>0.04491235975021561</v>
       </c>
       <c r="AD8">
-        <v>451.5</v>
+        <v>326.4</v>
       </c>
       <c r="AE8">
-        <v>85.52191810887686</v>
+        <v>8.595579300796407</v>
       </c>
       <c r="AF8">
-        <v>537.0219181088769</v>
+        <v>334.9955793007964</v>
       </c>
       <c r="AG8">
-        <v>437.6219181088769</v>
+        <v>102.0955793007964</v>
       </c>
       <c r="AH8">
-        <v>0.3720993364711108</v>
+        <v>0.4906235328058834</v>
       </c>
       <c r="AI8">
-        <v>0.288423436496371</v>
+        <v>0.3213708748894543</v>
       </c>
       <c r="AJ8">
-        <v>0.325654695917395</v>
+        <v>0.2269317237112396</v>
       </c>
       <c r="AK8">
-        <v>0.2482930360255773</v>
+        <v>0.1261224667699627</v>
       </c>
       <c r="AL8">
-        <v>24</v>
+        <v>27.2</v>
       </c>
       <c r="AM8">
-        <v>24</v>
+        <v>27.2</v>
       </c>
       <c r="AN8">
-        <v>-501.6666666666675</v>
+        <v>2.577384712571067</v>
       </c>
       <c r="AO8">
-        <v>-1.858333333333333</v>
+        <v>4.474264705882353</v>
       </c>
       <c r="AP8">
-        <v>-486.2465756765307</v>
+        <v>0.806187454996813</v>
       </c>
       <c r="AQ8">
-        <v>-1.858333333333333</v>
+        <v>4.474264705882353</v>
       </c>
     </row>
     <row r="9">
@@ -1517,7 +1508,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>James River Group Holdings, Ltd. (NasdaqGS:JRVR)</t>
+          <t>Lancashire Holdings Limited (LSE:LRE)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1526,118 +1517,118 @@
         </is>
       </c>
       <c r="D9">
-        <v>0.006840000000000001</v>
+        <v>0.219</v>
       </c>
       <c r="G9">
-        <v>-0.2260782094806991</v>
+        <v>0.02423469387755102</v>
       </c>
       <c r="H9">
-        <v>-0.2260782094806991</v>
+        <v>0.02423469387755102</v>
       </c>
       <c r="I9">
-        <v>-0.03687458087354664</v>
+        <v>0.1363998724489796</v>
       </c>
       <c r="J9">
-        <v>-0.03687458087354664</v>
+        <v>0.1307470765071186</v>
       </c>
       <c r="K9">
-        <v>-53</v>
+        <v>124.9</v>
       </c>
       <c r="L9">
-        <v>-0.0666415189236766</v>
+        <v>0.09956951530612244</v>
       </c>
       <c r="M9">
-        <v>18.36</v>
+        <v>47.4</v>
       </c>
       <c r="N9">
-        <v>0.02343929528916125</v>
+        <v>0.02496707927311035</v>
       </c>
       <c r="O9">
-        <v>-0.3464150943396227</v>
+        <v>0.3795036028823058</v>
       </c>
       <c r="P9">
-        <v>17.1</v>
+        <v>35.8</v>
       </c>
       <c r="Q9">
-        <v>0.0218307162006894</v>
+        <v>0.01885699236239136</v>
       </c>
       <c r="R9">
-        <v>-0.3226415094339623</v>
+        <v>0.2866293034427542</v>
       </c>
       <c r="S9">
-        <v>1.260000000000002</v>
+        <v>11.6</v>
       </c>
       <c r="T9">
-        <v>0.06862745098039223</v>
+        <v>0.2447257383966245</v>
       </c>
       <c r="U9">
-        <v>187.5</v>
+        <v>620.3</v>
       </c>
       <c r="V9">
-        <v>0.2393718881654538</v>
+        <v>0.3267316302343956</v>
       </c>
       <c r="W9">
-        <v>-0.0651425762045231</v>
+        <v>0.09098856268667589</v>
       </c>
       <c r="X9">
-        <v>0.1119530804526386</v>
+        <v>0.08688056413060978</v>
       </c>
       <c r="Y9">
-        <v>-0.1770956566571617</v>
+        <v>0.004107998556066111</v>
       </c>
       <c r="Z9">
-        <v>1.007369681443214</v>
+        <v>0.8692398309195483</v>
       </c>
       <c r="AA9">
-        <v>-0.0371463347879367</v>
+        <v>0.113650566676273</v>
       </c>
       <c r="AB9">
-        <v>0.09789830850826893</v>
+        <v>0.08041337062157548</v>
       </c>
       <c r="AC9">
-        <v>-0.1350446432962056</v>
+        <v>0.03323719605469752</v>
       </c>
       <c r="AD9">
-        <v>326.4</v>
+        <v>469.5</v>
       </c>
       <c r="AE9">
-        <v>11.88177084365821</v>
+        <v>0</v>
       </c>
       <c r="AF9">
-        <v>338.2817708436582</v>
+        <v>469.5</v>
       </c>
       <c r="AG9">
-        <v>150.7817708436582</v>
+        <v>-150.8</v>
       </c>
       <c r="AH9">
-        <v>0.3016113311017897</v>
+        <v>0.1982685810810811</v>
       </c>
       <c r="AI9">
-        <v>0.3349384915740455</v>
+        <v>0.2422350634609431</v>
       </c>
       <c r="AJ9">
-        <v>0.1614224530979475</v>
+        <v>-0.08628483149281911</v>
       </c>
       <c r="AK9">
-        <v>0.1833253649974445</v>
+        <v>-0.1144244631610896</v>
       </c>
       <c r="AL9">
-        <v>13.5</v>
+        <v>27.4</v>
       </c>
       <c r="AM9">
-        <v>13.5</v>
+        <v>27.4</v>
       </c>
       <c r="AN9">
-        <v>-14.66966292134831</v>
+        <v>2.732828870779977</v>
       </c>
       <c r="AO9">
-        <v>-2.303703703703704</v>
+        <v>6.244525547445256</v>
       </c>
       <c r="AP9">
-        <v>-6.776708801962166</v>
+        <v>-0.8777648428405119</v>
       </c>
       <c r="AQ9">
-        <v>-2.303703703703704</v>
+        <v>6.244525547445256</v>
       </c>
     </row>
     <row r="10">
@@ -1657,121 +1648,255 @@
         </is>
       </c>
       <c r="D10">
-        <v>0.388</v>
+        <v>0.314</v>
       </c>
       <c r="E10">
-        <v>0.0677</v>
+        <v>0.695</v>
       </c>
       <c r="G10">
-        <v>-0.1257147213539681</v>
+        <v>-0.05611780455153949</v>
       </c>
       <c r="H10">
-        <v>-0.1257147213539681</v>
+        <v>-0.05611780455153949</v>
       </c>
       <c r="I10">
-        <v>-0.1427672777425823</v>
+        <v>0.2354954399368633</v>
       </c>
       <c r="J10">
-        <v>-0.1427672777425823</v>
+        <v>0.1796728711138588</v>
       </c>
       <c r="K10">
-        <v>785.2</v>
+        <v>263.1</v>
       </c>
       <c r="L10">
-        <v>0.5986124876114965</v>
+        <v>0.1408835341365462</v>
       </c>
       <c r="M10">
-        <v>619</v>
+        <v>40.6</v>
       </c>
       <c r="N10">
-        <v>0.1724522204268123</v>
+        <v>0.01069293370907846</v>
       </c>
       <c r="O10">
-        <v>0.7883341823739174</v>
+        <v>0.1543139490687951</v>
       </c>
       <c r="P10">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="Q10">
-        <v>0.0008357942831671031</v>
+        <v>0.0006847691537833496</v>
       </c>
       <c r="R10">
-        <v>0.003820682628629648</v>
+        <v>0.009882174078297225</v>
       </c>
       <c r="S10">
-        <v>616</v>
+        <v>38</v>
       </c>
       <c r="T10">
-        <v>0.9951534733441034</v>
+        <v>0.9359605911330049</v>
       </c>
       <c r="U10">
-        <v>236.8</v>
+        <v>162.8</v>
       </c>
       <c r="V10">
-        <v>0.06597202875132334</v>
+        <v>0.04287708393689589</v>
       </c>
       <c r="W10">
-        <v>0.2229605020302695</v>
+        <v>0.07095469255663431</v>
       </c>
       <c r="X10">
-        <v>0.09925967221470011</v>
+        <v>0.08334027600707691</v>
       </c>
       <c r="Y10">
-        <v>0.1237008298155694</v>
+        <v>-0.01238558345044261</v>
       </c>
       <c r="Z10">
-        <v>0.3863009455016282</v>
+        <v>0.4743747064277103</v>
       </c>
       <c r="AA10">
-        <v>-0.05515113437865309</v>
+        <v>0.08523226548766062</v>
       </c>
       <c r="AB10">
-        <v>0.0928114043713798</v>
+        <v>0.07942803006984225</v>
       </c>
       <c r="AC10">
-        <v>-0.1479625387500329</v>
+        <v>0.005804235417818368</v>
       </c>
       <c r="AD10">
-        <v>615.5</v>
+        <v>564.7</v>
       </c>
       <c r="AE10">
-        <v>42.83919107472605</v>
+        <v>25.56132958953911</v>
       </c>
       <c r="AF10">
-        <v>658.339191074726</v>
+        <v>590.2613295895392</v>
       </c>
       <c r="AG10">
-        <v>421.539191074726</v>
+        <v>427.4613295895392</v>
       </c>
       <c r="AH10">
-        <v>0.1549857845458159</v>
+        <v>0.1345428821157037</v>
       </c>
       <c r="AI10">
-        <v>0.1455009257695866</v>
+        <v>0.1241489390009399</v>
       </c>
       <c r="AJ10">
-        <v>0.1050973776946678</v>
+        <v>0.1011895754739033</v>
       </c>
       <c r="AK10">
-        <v>0.09831040118112949</v>
+        <v>0.09309513461606959</v>
       </c>
       <c r="AL10">
-        <v>56.5</v>
+        <v>57.7</v>
       </c>
       <c r="AM10">
-        <v>56.5</v>
+        <v>57.7</v>
       </c>
       <c r="AN10">
-        <v>-5.057518488085456</v>
+        <v>1.267849124382578</v>
       </c>
       <c r="AO10">
-        <v>-3.355752212389381</v>
+        <v>7.559792027729635</v>
       </c>
       <c r="AP10">
-        <v>-3.463756705626344</v>
+        <v>0.959724583721462</v>
       </c>
       <c r="AQ10">
-        <v>-3.355752212389381</v>
+        <v>7.559792027729635</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Bermuda</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Assured Guaranty Ltd. (NYSE:AGO)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>0.0174</v>
+      </c>
+      <c r="E11">
+        <v>-0.0118</v>
+      </c>
+      <c r="G11">
+        <v>0.3096026490066225</v>
+      </c>
+      <c r="H11">
+        <v>0.3096026490066225</v>
+      </c>
+      <c r="I11">
+        <v>0.4213467076832213</v>
+      </c>
+      <c r="J11">
+        <v>0.3460263227699375</v>
+      </c>
+      <c r="K11">
+        <v>457</v>
+      </c>
+      <c r="L11">
+        <v>0.3783112582781457</v>
+      </c>
+      <c r="M11">
+        <v>256</v>
+      </c>
+      <c r="N11">
+        <v>0.05979073243647234</v>
+      </c>
+      <c r="O11">
+        <v>0.5601750547045952</v>
+      </c>
+      <c r="P11">
+        <v>66</v>
+      </c>
+      <c r="Q11">
+        <v>0.01541479820627803</v>
+      </c>
+      <c r="R11">
+        <v>0.1444201312910285</v>
+      </c>
+      <c r="S11">
+        <v>190</v>
+      </c>
+      <c r="T11">
+        <v>0.7421875</v>
+      </c>
+      <c r="U11">
+        <v>115</v>
+      </c>
+      <c r="V11">
+        <v>0.02685911808669656</v>
+      </c>
+      <c r="W11">
+        <v>0.09271657537025765</v>
+      </c>
+      <c r="X11">
+        <v>0.09349086124189612</v>
+      </c>
+      <c r="Y11">
+        <v>-0.0007742858716384693</v>
+      </c>
+      <c r="Z11">
+        <v>0.1805662336751206</v>
+      </c>
+      <c r="AA11">
+        <v>0.06248066985501922</v>
+      </c>
+      <c r="AB11">
+        <v>0.08323317960265129</v>
+      </c>
+      <c r="AC11">
+        <v>-0.02075250974763208</v>
+      </c>
+      <c r="AD11">
+        <v>1693</v>
+      </c>
+      <c r="AE11">
+        <v>100.0658855933434</v>
+      </c>
+      <c r="AF11">
+        <v>1793.065885593343</v>
+      </c>
+      <c r="AG11">
+        <v>1678.065885593343</v>
+      </c>
+      <c r="AH11">
+        <v>0.2951711121834326</v>
+      </c>
+      <c r="AI11">
+        <v>0.2527557418425883</v>
+      </c>
+      <c r="AJ11">
+        <v>0.2815704634801478</v>
+      </c>
+      <c r="AK11">
+        <v>0.2404427631292778</v>
+      </c>
+      <c r="AL11">
+        <v>88</v>
+      </c>
+      <c r="AM11">
+        <v>88</v>
+      </c>
+      <c r="AN11">
+        <v>3.182330827067669</v>
+      </c>
+      <c r="AO11">
+        <v>5.75</v>
+      </c>
+      <c r="AP11">
+        <v>3.154259183446134</v>
+      </c>
+      <c r="AQ11">
+        <v>5.75</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/bermuda/bermuda_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/bermuda/bermuda_insurance_prop_cas.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ5"/>
+  <dimension ref="A1:AQ11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -591,121 +591,121 @@
         <v>0.0601</v>
       </c>
       <c r="E2">
-        <v>0.316</v>
+        <v>0.3405</v>
       </c>
       <c r="F2">
-        <v>0.19915</v>
+        <v>0.09230000000000001</v>
       </c>
       <c r="G2">
-        <v>0.218978916446659</v>
+        <v>0.2406022162119723</v>
       </c>
       <c r="H2">
-        <v>0.218978916446659</v>
+        <v>0.2406022162119723</v>
       </c>
       <c r="I2">
-        <v>0.2912699232403042</v>
+        <v>0.2618129707060661</v>
       </c>
       <c r="J2">
-        <v>0.2912699232403042</v>
+        <v>0.2500237494239597</v>
       </c>
       <c r="K2">
-        <v>7165.8</v>
+        <v>9612.5</v>
       </c>
       <c r="L2">
-        <v>0.3330699438515599</v>
+        <v>0.2602411138996505</v>
       </c>
       <c r="M2">
-        <v>861.9</v>
+        <v>1629.19</v>
       </c>
       <c r="N2">
-        <v>0.01968122759345101</v>
+        <v>0.0261706338369803</v>
       </c>
       <c r="O2">
-        <v>0.1202796617265344</v>
+        <v>0.1694866059817945</v>
       </c>
       <c r="P2">
-        <v>195.2</v>
+        <v>561.03</v>
       </c>
       <c r="Q2">
-        <v>0.004457333363779599</v>
+        <v>0.009012153709242667</v>
       </c>
       <c r="R2">
-        <v>0.02724050350274917</v>
+        <v>0.05836462938881664</v>
       </c>
       <c r="S2">
-        <v>666.7</v>
+        <v>1068.16</v>
       </c>
       <c r="T2">
-        <v>0.773523610627683</v>
+        <v>0.655638691619762</v>
       </c>
       <c r="U2">
-        <v>2281.8</v>
+        <v>6360</v>
       </c>
       <c r="V2">
-        <v>0.05210421756901788</v>
+        <v>0.1021644075910083</v>
       </c>
       <c r="W2">
-        <v>0.2534280289712397</v>
+        <v>0.2147122818388038</v>
       </c>
       <c r="X2">
-        <v>0.08726337316778811</v>
+        <v>0.0891714367427844</v>
       </c>
       <c r="Y2">
-        <v>0.1661646558034516</v>
+        <v>0.1255408450960194</v>
       </c>
       <c r="Z2">
-        <v>0.805601380965034</v>
+        <v>0.8861445602838182</v>
       </c>
       <c r="AA2">
-        <v>0.2832940251572328</v>
+        <v>0.2429150987735511</v>
       </c>
       <c r="AB2">
-        <v>0.08433802595799632</v>
+        <v>0.08432325400867363</v>
       </c>
       <c r="AC2">
-        <v>0.1989559991992365</v>
+        <v>0.159545075007775</v>
       </c>
       <c r="AD2">
-        <v>5114.3</v>
+        <v>8481.9</v>
       </c>
       <c r="AE2">
-        <v>226.0118171939998</v>
+        <v>399.102411635521</v>
       </c>
       <c r="AF2">
-        <v>5340.311817194</v>
+        <v>8881.002411635522</v>
       </c>
       <c r="AG2">
-        <v>3058.511817193999</v>
+        <v>2521.002411635522</v>
       </c>
       <c r="AH2">
-        <v>0.108690247404108</v>
+        <v>0.1248496084908365</v>
       </c>
       <c r="AI2">
-        <v>0.1452596188280597</v>
+        <v>0.1508058550889835</v>
       </c>
       <c r="AJ2">
-        <v>0.06528096316566584</v>
+        <v>0.03892021313890463</v>
       </c>
       <c r="AK2">
-        <v>0.08869850644324277</v>
+        <v>0.04799139346049371</v>
       </c>
       <c r="AL2">
-        <v>280.4</v>
+        <v>525.3</v>
       </c>
       <c r="AM2">
-        <v>280.4</v>
+        <v>525.3</v>
       </c>
       <c r="AN2">
-        <v>0.7868638070035079</v>
+        <v>0.9434942401900804</v>
       </c>
       <c r="AO2">
-        <v>22.33844507845934</v>
+        <v>18.40814772510946</v>
       </c>
       <c r="AP2">
-        <v>0.4705692376752414</v>
+        <v>0.2804267033192347</v>
       </c>
       <c r="AQ2">
-        <v>22.33844507845934</v>
+        <v>18.40814772510946</v>
       </c>
     </row>
     <row r="3">
@@ -716,7 +716,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Arch Capital Group Ltd. (NasdaqGS:ACGL)</t>
+          <t>Hamilton Insurance Group, Ltd. (NYSE:HG)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -724,41 +724,35 @@
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>0.209</v>
-      </c>
-      <c r="E3">
-        <v>0.316</v>
-      </c>
       <c r="F3">
-        <v>0.09230000000000001</v>
+        <v>-2.18</v>
       </c>
       <c r="G3">
-        <v>0.2181182190075295</v>
+        <v>0.1302774959191777</v>
       </c>
       <c r="H3">
-        <v>0.2181182190075295</v>
+        <v>0.1302774959191777</v>
       </c>
       <c r="I3">
-        <v>0.2973325993995758</v>
+        <v>0.3011856147315635</v>
       </c>
       <c r="J3">
-        <v>0.2973325993995758</v>
+        <v>0.3011856147315635</v>
       </c>
       <c r="K3">
-        <v>5711</v>
+        <v>493.4</v>
       </c>
       <c r="L3">
-        <v>0.3385901464397937</v>
+        <v>0.2176732695107425</v>
       </c>
       <c r="M3">
-        <v>5</v>
+        <v>123.6</v>
       </c>
       <c r="N3">
-        <v>0.0001444873732484518</v>
+        <v>0.06405804612593936</v>
       </c>
       <c r="O3">
-        <v>0.0008755034144633164</v>
+        <v>0.2505066882853668</v>
       </c>
       <c r="P3">
         <v>-0</v>
@@ -770,79 +764,79 @@
         <v>-0</v>
       </c>
       <c r="S3">
-        <v>5</v>
+        <v>123.6</v>
       </c>
       <c r="T3">
         <v>1</v>
       </c>
       <c r="U3">
-        <v>1025</v>
+        <v>957.4</v>
       </c>
       <c r="V3">
-        <v>0.02961991151593263</v>
+        <v>0.4961907229852293</v>
       </c>
       <c r="W3">
-        <v>0.3963495037823582</v>
+        <v>0.2741568039117631</v>
       </c>
       <c r="X3">
-        <v>0.08486110640690731</v>
+        <v>0.08477423802126265</v>
       </c>
       <c r="Y3">
-        <v>0.3114883973754509</v>
+        <v>0.1893825658905004</v>
       </c>
       <c r="Z3">
-        <v>0.9777712979436052</v>
+        <v>1.968624919083996</v>
       </c>
       <c r="AA3">
-        <v>0.2907232816358692</v>
+        <v>0.5929215064301877</v>
       </c>
       <c r="AB3">
-        <v>0.08323829388014126</v>
+        <v>0.08319349825505222</v>
       </c>
       <c r="AC3">
-        <v>0.207484987755728</v>
+        <v>0.5097280081751355</v>
       </c>
       <c r="AD3">
-        <v>2727</v>
+        <v>149.9</v>
       </c>
       <c r="AE3">
-        <v>144.4552296367732</v>
+        <v>6.412835439825034</v>
       </c>
       <c r="AF3">
-        <v>2871.455229636773</v>
+        <v>156.3128354398251</v>
       </c>
       <c r="AG3">
-        <v>1846.455229636773</v>
+        <v>-801.0871645601749</v>
       </c>
       <c r="AH3">
-        <v>0.07662004183794359</v>
+        <v>0.07494096919144912</v>
       </c>
       <c r="AI3">
-        <v>0.1141938057360138</v>
+        <v>0.06178341597727553</v>
       </c>
       <c r="AJ3">
-        <v>0.05065504662296332</v>
+        <v>-0.7099238323072889</v>
       </c>
       <c r="AK3">
-        <v>0.07655142542119338</v>
+        <v>-0.5093988466246548</v>
       </c>
       <c r="AL3">
-        <v>138</v>
+        <v>22.5</v>
       </c>
       <c r="AM3">
-        <v>138</v>
+        <v>22.5</v>
       </c>
       <c r="AN3">
-        <v>0.5240199846272099</v>
+        <v>0.2139961169483783</v>
       </c>
       <c r="AO3">
-        <v>36.31884057971015</v>
+        <v>30.26222222222222</v>
       </c>
       <c r="AP3">
-        <v>0.3548146098456521</v>
+        <v>-1.143626034376677</v>
       </c>
       <c r="AQ3">
-        <v>36.31884057971015</v>
+        <v>30.26222222222222</v>
       </c>
     </row>
     <row r="4">
@@ -853,7 +847,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hiscox Ltd (LSE:HSX)</t>
+          <t>Lancashire Holdings Limited (LSE:LRE)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -862,124 +856,121 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0601</v>
+        <v>0.247</v>
       </c>
       <c r="E4">
-        <v>0.444</v>
-      </c>
-      <c r="F4">
-        <v>0.306</v>
+        <v>2.399</v>
       </c>
       <c r="G4">
-        <v>0.1913025076711459</v>
+        <v>0.2728142478657639</v>
       </c>
       <c r="H4">
-        <v>0.1913025076711459</v>
+        <v>0.2728142478657639</v>
       </c>
       <c r="I4">
-        <v>0.1906412019892075</v>
+        <v>0.3076243744480424</v>
       </c>
       <c r="J4">
-        <v>0.1906412019892075</v>
+        <v>0.2946410191561176</v>
       </c>
       <c r="K4">
-        <v>720.8</v>
+        <v>363.1</v>
       </c>
       <c r="L4">
-        <v>0.190667654216485</v>
+        <v>0.2672210774212541</v>
       </c>
       <c r="M4">
-        <v>253.9</v>
+        <v>167.8</v>
       </c>
       <c r="N4">
-        <v>0.05509743500716115</v>
+        <v>0.08473035750353464</v>
       </c>
       <c r="O4">
-        <v>0.3522475027746948</v>
+        <v>0.4621316441751583</v>
       </c>
       <c r="P4">
-        <v>127.2</v>
+        <v>167.8</v>
       </c>
       <c r="Q4">
-        <v>0.0276029686211536</v>
+        <v>0.08473035750353464</v>
       </c>
       <c r="R4">
-        <v>0.1764705882352941</v>
+        <v>0.4621316441751583</v>
       </c>
       <c r="S4">
-        <v>126.7</v>
+        <v>0</v>
       </c>
       <c r="T4">
-        <v>0.4990153603781016</v>
+        <v>0</v>
       </c>
       <c r="U4">
-        <v>1109.8</v>
+        <v>698.2</v>
       </c>
       <c r="V4">
-        <v>0.2408315611301593</v>
+        <v>0.3525550393859826</v>
       </c>
       <c r="W4">
-        <v>0.2534280289712397</v>
+        <v>0.2472254374617008</v>
       </c>
       <c r="X4">
-        <v>0.08726337316778811</v>
+        <v>0.09041535094586967</v>
       </c>
       <c r="Y4">
-        <v>0.1661646558034516</v>
+        <v>0.1568100865158312</v>
       </c>
       <c r="Z4">
-        <v>1.486006289308176</v>
+        <v>1.031034221109341</v>
       </c>
       <c r="AA4">
-        <v>0.2832940251572328</v>
+        <v>0.30378497369249</v>
       </c>
       <c r="AB4">
-        <v>0.08433802595799632</v>
+        <v>0.08461326768144899</v>
       </c>
       <c r="AC4">
-        <v>0.1989559991992365</v>
+        <v>0.219171706011041</v>
       </c>
       <c r="AD4">
-        <v>689.3</v>
+        <v>470.3</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>689.3</v>
+        <v>470.3</v>
       </c>
       <c r="AG4">
-        <v>-420.5</v>
+        <v>-227.9</v>
       </c>
       <c r="AH4">
-        <v>0.1301179801793299</v>
+        <v>0.1919043538580814</v>
       </c>
       <c r="AI4">
-        <v>0.1699080578767039</v>
+        <v>0.2314696328378777</v>
       </c>
       <c r="AJ4">
-        <v>-0.1004131145975118</v>
+        <v>-0.1300427960057061</v>
       </c>
       <c r="AK4">
-        <v>-0.1426826371687422</v>
+        <v>-0.1708908218356329</v>
       </c>
       <c r="AL4">
-        <v>51.4</v>
+        <v>28.1</v>
       </c>
       <c r="AM4">
-        <v>51.4</v>
+        <v>28.1</v>
       </c>
       <c r="AN4">
-        <v>0.9251107233928331</v>
+        <v>1.118430439952438</v>
       </c>
       <c r="AO4">
-        <v>14.02140077821012</v>
+        <v>14.87544483985765</v>
       </c>
       <c r="AP4">
-        <v>-0.5643537780163737</v>
+        <v>-0.5419738406658741</v>
       </c>
       <c r="AQ4">
-        <v>14.02140077821012</v>
+        <v>14.87544483985765</v>
       </c>
     </row>
     <row r="5">
@@ -990,130 +981,937 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>Arch Capital Group Ltd. (NasdaqGS:ACGL)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.209</v>
+      </c>
+      <c r="E5">
+        <v>0.316</v>
+      </c>
+      <c r="F5">
+        <v>0.09230000000000001</v>
+      </c>
+      <c r="G5">
+        <v>0.2181182190075295</v>
+      </c>
+      <c r="H5">
+        <v>0.2181182190075295</v>
+      </c>
+      <c r="I5">
+        <v>0.2973325993995758</v>
+      </c>
+      <c r="J5">
+        <v>0.2973325993995758</v>
+      </c>
+      <c r="K5">
+        <v>5711</v>
+      </c>
+      <c r="L5">
+        <v>0.3385901464397937</v>
+      </c>
+      <c r="M5">
+        <v>5</v>
+      </c>
+      <c r="N5">
+        <v>0.0001444873732484518</v>
+      </c>
+      <c r="O5">
+        <v>0.0008755034144633164</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>-0</v>
+      </c>
+      <c r="S5">
+        <v>5</v>
+      </c>
+      <c r="T5">
+        <v>1</v>
+      </c>
+      <c r="U5">
+        <v>1025</v>
+      </c>
+      <c r="V5">
+        <v>0.02961991151593263</v>
+      </c>
+      <c r="W5">
+        <v>0.3963495037823582</v>
+      </c>
+      <c r="X5">
+        <v>0.08484510871365858</v>
+      </c>
+      <c r="Y5">
+        <v>0.3115043950686996</v>
+      </c>
+      <c r="Z5">
+        <v>0.9777712979436052</v>
+      </c>
+      <c r="AA5">
+        <v>0.2907232816358692</v>
+      </c>
+      <c r="AB5">
+        <v>0.08322352193081857</v>
+      </c>
+      <c r="AC5">
+        <v>0.2074997597050507</v>
+      </c>
+      <c r="AD5">
+        <v>2727</v>
+      </c>
+      <c r="AE5">
+        <v>144.4552296367732</v>
+      </c>
+      <c r="AF5">
+        <v>2871.455229636773</v>
+      </c>
+      <c r="AG5">
+        <v>1846.455229636773</v>
+      </c>
+      <c r="AH5">
+        <v>0.07662004183794359</v>
+      </c>
+      <c r="AI5">
+        <v>0.1141938057360138</v>
+      </c>
+      <c r="AJ5">
+        <v>0.05065504662296332</v>
+      </c>
+      <c r="AK5">
+        <v>0.07655142542119338</v>
+      </c>
+      <c r="AL5">
+        <v>138</v>
+      </c>
+      <c r="AM5">
+        <v>138</v>
+      </c>
+      <c r="AN5">
+        <v>0.5240199846272099</v>
+      </c>
+      <c r="AO5">
+        <v>36.31884057971015</v>
+      </c>
+      <c r="AP5">
+        <v>0.3548146098456521</v>
+      </c>
+      <c r="AQ5">
+        <v>36.31884057971015</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Bermuda</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Hiscox Ltd (LSE:HSX)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D6">
+        <v>0.0601</v>
+      </c>
+      <c r="E6">
+        <v>0.444</v>
+      </c>
+      <c r="F6">
+        <v>0.306</v>
+      </c>
+      <c r="G6">
+        <v>0.1913025076711459</v>
+      </c>
+      <c r="H6">
+        <v>0.1913025076711459</v>
+      </c>
+      <c r="I6">
+        <v>0.1906412019892075</v>
+      </c>
+      <c r="J6">
+        <v>0.1906412019892075</v>
+      </c>
+      <c r="K6">
+        <v>720.8</v>
+      </c>
+      <c r="L6">
+        <v>0.190667654216485</v>
+      </c>
+      <c r="M6">
+        <v>253.9</v>
+      </c>
+      <c r="N6">
+        <v>0.05509743500716115</v>
+      </c>
+      <c r="O6">
+        <v>0.3522475027746948</v>
+      </c>
+      <c r="P6">
+        <v>127.2</v>
+      </c>
+      <c r="Q6">
+        <v>0.0276029686211536</v>
+      </c>
+      <c r="R6">
+        <v>0.1764705882352941</v>
+      </c>
+      <c r="S6">
+        <v>126.7</v>
+      </c>
+      <c r="T6">
+        <v>0.4990153603781016</v>
+      </c>
+      <c r="U6">
+        <v>1109.8</v>
+      </c>
+      <c r="V6">
+        <v>0.2408315611301593</v>
+      </c>
+      <c r="W6">
+        <v>0.2534280289712397</v>
+      </c>
+      <c r="X6">
+        <v>0.08724639161283455</v>
+      </c>
+      <c r="Y6">
+        <v>0.1661816373584052</v>
+      </c>
+      <c r="Z6">
+        <v>1.486006289308176</v>
+      </c>
+      <c r="AA6">
+        <v>0.2832940251572328</v>
+      </c>
+      <c r="AB6">
+        <v>0.08432325400867363</v>
+      </c>
+      <c r="AC6">
+        <v>0.1989707711485592</v>
+      </c>
+      <c r="AD6">
+        <v>689.3</v>
+      </c>
+      <c r="AE6">
+        <v>0</v>
+      </c>
+      <c r="AF6">
+        <v>689.3</v>
+      </c>
+      <c r="AG6">
+        <v>-420.5</v>
+      </c>
+      <c r="AH6">
+        <v>0.1301179801793299</v>
+      </c>
+      <c r="AI6">
+        <v>0.1699080578767039</v>
+      </c>
+      <c r="AJ6">
+        <v>-0.1004131145975118</v>
+      </c>
+      <c r="AK6">
+        <v>-0.1426826371687422</v>
+      </c>
+      <c r="AL6">
+        <v>51.4</v>
+      </c>
+      <c r="AM6">
+        <v>51.4</v>
+      </c>
+      <c r="AN6">
+        <v>0.9251107233928331</v>
+      </c>
+      <c r="AO6">
+        <v>14.02140077821012</v>
+      </c>
+      <c r="AP6">
+        <v>-0.5643537780163737</v>
+      </c>
+      <c r="AQ6">
+        <v>14.02140077821012</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Bermuda</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>White Mountains Insurance Group, Ltd. (NYSE:WTM)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D7">
+        <v>0.304</v>
+      </c>
+      <c r="E7">
+        <v>0.245</v>
+      </c>
+      <c r="G7">
+        <v>0.2492042003585672</v>
+      </c>
+      <c r="H7">
+        <v>0.2492042003585672</v>
+      </c>
+      <c r="I7">
+        <v>0.3748963124344138</v>
+      </c>
+      <c r="J7">
+        <v>0.3748963124344138</v>
+      </c>
+      <c r="K7">
+        <v>647.3</v>
+      </c>
+      <c r="L7">
+        <v>0.2368372909882551</v>
+      </c>
+      <c r="M7">
+        <v>10.6</v>
+      </c>
+      <c r="N7">
+        <v>0.002151672620980838</v>
+      </c>
+      <c r="O7">
+        <v>0.01637571450641125</v>
+      </c>
+      <c r="P7">
+        <v>2.5</v>
+      </c>
+      <c r="Q7">
+        <v>0.0005074699577784995</v>
+      </c>
+      <c r="R7">
+        <v>0.003862196817549823</v>
+      </c>
+      <c r="S7">
+        <v>8.1</v>
+      </c>
+      <c r="T7">
+        <v>0.7641509433962264</v>
+      </c>
+      <c r="U7">
+        <v>275</v>
+      </c>
+      <c r="V7">
+        <v>0.05582169535563495</v>
+      </c>
+      <c r="W7">
+        <v>0.1639107644779823</v>
+      </c>
+      <c r="X7">
+        <v>0.08610367655062363</v>
+      </c>
+      <c r="Y7">
+        <v>0.07780708792735867</v>
+      </c>
+      <c r="Z7">
+        <v>0.6479527557797673</v>
+      </c>
+      <c r="AA7">
+        <v>0.2429150987735511</v>
+      </c>
+      <c r="AB7">
+        <v>0.08337002376577606</v>
+      </c>
+      <c r="AC7">
+        <v>0.159545075007775</v>
+      </c>
+      <c r="AD7">
+        <v>544.9</v>
+      </c>
+      <c r="AE7">
+        <v>35.85444242751766</v>
+      </c>
+      <c r="AF7">
+        <v>580.7544424275177</v>
+      </c>
+      <c r="AG7">
+        <v>305.7544424275177</v>
+      </c>
+      <c r="AH7">
+        <v>0.105454540724942</v>
+      </c>
+      <c r="AI7">
+        <v>0.09943481362124551</v>
+      </c>
+      <c r="AJ7">
+        <v>0.05843757973735567</v>
+      </c>
+      <c r="AK7">
+        <v>0.05493692418075733</v>
+      </c>
+      <c r="AL7">
+        <v>64.5</v>
+      </c>
+      <c r="AM7">
+        <v>64.5</v>
+      </c>
+      <c r="AN7">
+        <v>66.45121951219512</v>
+      </c>
+      <c r="AO7">
+        <v>15.86976744186047</v>
+      </c>
+      <c r="AP7">
+        <v>37.28712712530704</v>
+      </c>
+      <c r="AQ7">
+        <v>15.86976744186047</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Bermuda</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Fidelis Insurance Holdings Limited (NYSE:FIHL)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="G8">
+        <v>0.9074742380103482</v>
+      </c>
+      <c r="H8">
+        <v>0.9074742380103482</v>
+      </c>
+      <c r="I8">
+        <v>0.1936712918110861</v>
+      </c>
+      <c r="J8">
+        <v>0.1936712918110861</v>
+      </c>
+      <c r="K8">
+        <v>463.8</v>
+      </c>
+      <c r="L8">
+        <v>0.2016609417800774</v>
+      </c>
+      <c r="M8">
+        <v>142.7</v>
+      </c>
+      <c r="N8">
+        <v>0.07044826224328593</v>
+      </c>
+      <c r="O8">
+        <v>0.3076757222940922</v>
+      </c>
+      <c r="P8">
+        <v>35</v>
+      </c>
+      <c r="Q8">
+        <v>0.01727883096366509</v>
+      </c>
+      <c r="R8">
+        <v>0.07546356188012074</v>
+      </c>
+      <c r="S8">
+        <v>107.7</v>
+      </c>
+      <c r="T8">
+        <v>0.7547302032235459</v>
+      </c>
+      <c r="U8">
+        <v>806.8</v>
+      </c>
+      <c r="V8">
+        <v>0.3983017377567141</v>
+      </c>
+      <c r="W8">
+        <v>0.2147122818388038</v>
+      </c>
+      <c r="X8">
+        <v>0.09103907824997312</v>
+      </c>
+      <c r="Y8">
+        <v>0.1236732035888307</v>
+      </c>
+      <c r="Z8">
+        <v>1.091874826793003</v>
+      </c>
+      <c r="AA8">
+        <v>0.2114648082010067</v>
+      </c>
+      <c r="AB8">
+        <v>0.08548415531186764</v>
+      </c>
+      <c r="AC8">
+        <v>0.1259806528891391</v>
+      </c>
+      <c r="AD8">
+        <v>507.2</v>
+      </c>
+      <c r="AE8">
+        <v>8.876979818415048</v>
+      </c>
+      <c r="AF8">
+        <v>516.076979818415</v>
+      </c>
+      <c r="AG8">
+        <v>-290.723020181585</v>
+      </c>
+      <c r="AH8">
+        <v>0.2030458566986294</v>
+      </c>
+      <c r="AI8">
+        <v>0.1639184199117668</v>
+      </c>
+      <c r="AJ8">
+        <v>-0.1675755823401462</v>
+      </c>
+      <c r="AK8">
+        <v>-0.1241569347013866</v>
+      </c>
+      <c r="AL8">
+        <v>35</v>
+      </c>
+      <c r="AM8">
+        <v>35</v>
+      </c>
+      <c r="AN8">
+        <v>1.133154602323503</v>
+      </c>
+      <c r="AO8">
+        <v>12.75714285714286</v>
+      </c>
+      <c r="AP8">
+        <v>-0.6495152372242738</v>
+      </c>
+      <c r="AQ8">
+        <v>12.75714285714286</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Bermuda</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>AXIS Capital Holdings Limited (NYSE:AXS)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D9">
+        <v>0.0326</v>
+      </c>
+      <c r="E9">
+        <v>0.365</v>
+      </c>
+      <c r="F9">
+        <v>0.2</v>
+      </c>
+      <c r="G9">
+        <v>0.1054933637216785</v>
+      </c>
+      <c r="H9">
+        <v>0.1054933637216785</v>
+      </c>
+      <c r="I9">
+        <v>0.1302165919382374</v>
+      </c>
+      <c r="J9">
+        <v>0.1302165919382374</v>
+      </c>
+      <c r="K9">
+        <v>645.6</v>
+      </c>
+      <c r="L9">
+        <v>0.1081914465746079</v>
+      </c>
+      <c r="M9">
+        <v>313.8</v>
+      </c>
+      <c r="N9">
+        <v>0.04232818506778175</v>
+      </c>
+      <c r="O9">
+        <v>0.4860594795539033</v>
+      </c>
+      <c r="P9">
+        <v>152.8</v>
+      </c>
+      <c r="Q9">
+        <v>0.0206110474135024</v>
+      </c>
+      <c r="R9">
+        <v>0.2366790582403965</v>
+      </c>
+      <c r="S9">
+        <v>161</v>
+      </c>
+      <c r="T9">
+        <v>0.5130656469088591</v>
+      </c>
+      <c r="U9">
+        <v>981</v>
+      </c>
+      <c r="V9">
+        <v>0.1323261617319755</v>
+      </c>
+      <c r="W9">
+        <v>0.1440042826552463</v>
+      </c>
+      <c r="X9">
+        <v>0.0891714367427844</v>
+      </c>
+      <c r="Y9">
+        <v>0.05483284591246186</v>
+      </c>
+      <c r="Z9">
+        <v>1.073960254293979</v>
+      </c>
+      <c r="AA9">
+        <v>0.1398474441912848</v>
+      </c>
+      <c r="AB9">
+        <v>0.08427996280464958</v>
+      </c>
+      <c r="AC9">
+        <v>0.05556748138663517</v>
+      </c>
+      <c r="AD9">
+        <v>1390.4</v>
+      </c>
+      <c r="AE9">
+        <v>114.3577629307487</v>
+      </c>
+      <c r="AF9">
+        <v>1504.757762930749</v>
+      </c>
+      <c r="AG9">
+        <v>523.7577629307489</v>
+      </c>
+      <c r="AH9">
+        <v>0.1687277720526717</v>
+      </c>
+      <c r="AI9">
+        <v>0.1983086635355171</v>
+      </c>
+      <c r="AJ9">
+        <v>0.06598724377792625</v>
+      </c>
+      <c r="AK9">
+        <v>0.07927366599335088</v>
+      </c>
+      <c r="AL9">
+        <v>69.3</v>
+      </c>
+      <c r="AM9">
+        <v>69.3</v>
+      </c>
+      <c r="AN9">
+        <v>1.625628434467439</v>
+      </c>
+      <c r="AO9">
+        <v>11.29004329004329</v>
+      </c>
+      <c r="AP9">
+        <v>0.6123673131424633</v>
+      </c>
+      <c r="AQ9">
+        <v>11.29004329004329</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Bermuda</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
           <t>Assured Guaranty Ltd. (NYSE:AGO)</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Insurance (Prop/Cas.)</t>
         </is>
       </c>
-      <c r="D5">
+      <c r="D10">
         <v>-0.0135</v>
       </c>
-      <c r="E5">
+      <c r="E10">
         <v>0.158</v>
       </c>
-      <c r="G5">
+      <c r="G10">
         <v>0.356401384083045</v>
       </c>
-      <c r="H5">
+      <c r="H10">
         <v>0.356401384083045</v>
       </c>
-      <c r="I5">
+      <c r="I10">
         <v>0.6120976729971797</v>
       </c>
-      <c r="J5">
+      <c r="J10">
         <v>0.6120976729971797</v>
       </c>
-      <c r="K5">
+      <c r="K10">
         <v>734</v>
       </c>
-      <c r="L5">
+      <c r="L10">
         <v>0.8465974625144176</v>
       </c>
-      <c r="M5">
+      <c r="M10">
         <v>603</v>
       </c>
-      <c r="N5">
+      <c r="N10">
         <v>0.1316680131886368</v>
       </c>
-      <c r="O5">
+      <c r="O10">
         <v>0.8215258855585831</v>
       </c>
-      <c r="P5">
+      <c r="P10">
         <v>68</v>
       </c>
-      <c r="Q5">
+      <c r="Q10">
         <v>0.01484813415725921</v>
       </c>
-      <c r="R5">
+      <c r="R10">
         <v>0.09264305177111716</v>
       </c>
-      <c r="S5">
+      <c r="S10">
         <v>535</v>
       </c>
-      <c r="T5">
+      <c r="T10">
         <v>0.8872305140961857</v>
       </c>
-      <c r="U5">
+      <c r="U10">
         <v>147</v>
       </c>
-      <c r="V5">
+      <c r="V10">
         <v>0.03209817236936918</v>
       </c>
-      <c r="W5">
+      <c r="W10">
         <v>0.1397562833206397</v>
       </c>
-      <c r="X5">
-        <v>0.09588345756841592</v>
-      </c>
-      <c r="Y5">
-        <v>0.04387282575222383</v>
-      </c>
-      <c r="Z5">
+      <c r="X10">
+        <v>0.09586294560998165</v>
+      </c>
+      <c r="Y10">
+        <v>0.04389333771065809</v>
+      </c>
+      <c r="Z10">
         <v>0.1254420750255952</v>
       </c>
-      <c r="AA5">
+      <c r="AA10">
         <v>0.07678280221910441</v>
       </c>
-      <c r="AB5">
-        <v>0.08659220428083567</v>
-      </c>
-      <c r="AC5">
-        <v>-0.009809402061731254</v>
-      </c>
-      <c r="AD5">
+      <c r="AB10">
+        <v>0.08657743233151297</v>
+      </c>
+      <c r="AC10">
+        <v>-0.009794630112408553</v>
+      </c>
+      <c r="AD10">
         <v>1698</v>
       </c>
-      <c r="AE5">
+      <c r="AE10">
         <v>81.55658755722655</v>
       </c>
-      <c r="AF5">
+      <c r="AF10">
         <v>1779.556587557227</v>
       </c>
-      <c r="AG5">
+      <c r="AG10">
         <v>1632.556587557227</v>
       </c>
-      <c r="AH5">
+      <c r="AH10">
         <v>0.2798372047196802</v>
       </c>
-      <c r="AI5">
+      <c r="AI10">
         <v>0.2353426264752871</v>
       </c>
-      <c r="AJ5">
+      <c r="AJ10">
         <v>0.2627960652538304</v>
       </c>
-      <c r="AK5">
+      <c r="AK10">
         <v>0.2201826324040616</v>
       </c>
-      <c r="AL5">
+      <c r="AL10">
         <v>91</v>
       </c>
-      <c r="AM5">
+      <c r="AM10">
         <v>91</v>
       </c>
-      <c r="AN5">
+      <c r="AN10">
         <v>3.084468664850136</v>
       </c>
-      <c r="AO5">
+      <c r="AO10">
         <v>5.835164835164835</v>
       </c>
-      <c r="AP5">
+      <c r="AP10">
         <v>2.965588714908677</v>
       </c>
-      <c r="AQ5">
+      <c r="AQ10">
         <v>5.835164835164835</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Bermuda</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>James River Group Holdings, Ltd. (NasdaqGS:JRVR)</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D11">
+        <v>-0.0198</v>
+      </c>
+      <c r="F11">
+        <v>0.06900000000000001</v>
+      </c>
+      <c r="G11">
+        <v>0.1408132530120482</v>
+      </c>
+      <c r="H11">
+        <v>0.1408132530120482</v>
+      </c>
+      <c r="I11">
+        <v>0.07063539813629149</v>
+      </c>
+      <c r="J11">
+        <v>0.04499069944986719</v>
+      </c>
+      <c r="K11">
+        <v>-166.5</v>
+      </c>
+      <c r="L11">
+        <v>-0.208960843373494</v>
+      </c>
+      <c r="M11">
+        <v>8.790000000000001</v>
+      </c>
+      <c r="N11">
+        <v>0.0477198697068404</v>
+      </c>
+      <c r="O11">
+        <v>-0.0527927927927928</v>
+      </c>
+      <c r="P11">
+        <v>7.73</v>
+      </c>
+      <c r="Q11">
+        <v>0.04196525515743757</v>
+      </c>
+      <c r="R11">
+        <v>-0.04642642642642643</v>
+      </c>
+      <c r="S11">
+        <v>1.06</v>
+      </c>
+      <c r="T11">
+        <v>0.1205915813424346</v>
+      </c>
+      <c r="U11">
+        <v>359.8</v>
+      </c>
+      <c r="V11">
+        <v>1.953311617806732</v>
+      </c>
+      <c r="W11">
+        <v>-0.296</v>
+      </c>
+      <c r="X11">
+        <v>0.1430168676338341</v>
+      </c>
+      <c r="Y11">
+        <v>-0.4390168676338341</v>
+      </c>
+      <c r="Z11">
+        <v>1.271444914236595</v>
+      </c>
+      <c r="AA11">
+        <v>0.05720319600348084</v>
+      </c>
+      <c r="AB11">
+        <v>0.09310325908442792</v>
+      </c>
+      <c r="AC11">
+        <v>-0.03590006308094708</v>
+      </c>
+      <c r="AD11">
+        <v>304.9</v>
+      </c>
+      <c r="AE11">
+        <v>7.588573825014708</v>
+      </c>
+      <c r="AF11">
+        <v>312.4885738250147</v>
+      </c>
+      <c r="AG11">
+        <v>-47.31142617498534</v>
+      </c>
+      <c r="AH11">
+        <v>0.6291438746386496</v>
+      </c>
+      <c r="AI11">
+        <v>0.3163837084951204</v>
+      </c>
+      <c r="AJ11">
+        <v>-0.3456199801998359</v>
+      </c>
+      <c r="AK11">
+        <v>-0.07535003525668632</v>
+      </c>
+      <c r="AL11">
+        <v>25.5</v>
+      </c>
+      <c r="AM11">
+        <v>25.5</v>
+      </c>
+      <c r="AN11">
+        <v>5.238831615120274</v>
+      </c>
+      <c r="AO11">
+        <v>2.145098039215686</v>
+      </c>
+      <c r="AP11">
+        <v>-0.8129111026629784</v>
+      </c>
+      <c r="AQ11">
+        <v>2.145098039215686</v>
       </c>
     </row>
   </sheetData>
